--- a/research/traditional_assets/database/data/estonia/estonia_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_furn_home_furnishings.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.1811320754716981</v>
+        <v>-0.09387040280210159</v>
       </c>
       <c r="H2">
-        <v>-0.2886792452830189</v>
+        <v>-0.1961471103327495</v>
       </c>
       <c r="I2">
-        <v>-0.4056603773584905</v>
+        <v>-0.3877408056042032</v>
       </c>
       <c r="J2">
-        <v>-0.4056603773584905</v>
+        <v>-0.3877408056042032</v>
       </c>
       <c r="K2">
-        <v>-0.392</v>
+        <v>-1.119</v>
       </c>
       <c r="L2">
-        <v>-0.369811320754717</v>
+        <v>-0.3919439579684764</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.46</v>
+        <v>1.722</v>
       </c>
       <c r="V2">
-        <v>0.04818481848184818</v>
+        <v>0.06888</v>
       </c>
       <c r="X2">
-        <v>0.06943301502953624</v>
+        <v>0.1178424621867519</v>
+      </c>
+      <c r="Z2">
+        <v>3.736910994764397</v>
       </c>
       <c r="AB2">
-        <v>0.06901348239604764</v>
+        <v>0.1166466076724133</v>
       </c>
       <c r="AD2">
-        <v>0.364</v>
+        <v>0.498</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.364</v>
+        <v>0.498</v>
       </c>
       <c r="AG2">
-        <v>-1.096</v>
+        <v>-1.224</v>
       </c>
       <c r="AH2">
-        <v>0.01187059744325593</v>
+        <v>0.01953094360341988</v>
       </c>
       <c r="AI2">
-        <v>0.1636690647482014</v>
+        <v>0.11985559566787</v>
       </c>
       <c r="AJ2">
-        <v>-0.03752910560197233</v>
+        <v>-0.05148048452220727</v>
       </c>
       <c r="AK2">
-        <v>-1.43455497382199</v>
+        <v>-0.5030826140567202</v>
       </c>
       <c r="AL2">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AM2">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AN2">
-        <v>-0.8687350835322196</v>
+        <v>-0.4806949806949807</v>
       </c>
       <c r="AO2">
-        <v>-35.83333333333333</v>
+        <v>-85.15384615384616</v>
       </c>
       <c r="AP2">
-        <v>2.615751789976134</v>
+        <v>1.181467181467181</v>
       </c>
       <c r="AQ2">
-        <v>-35.83333333333333</v>
+        <v>-85.15384615384616</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +701,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.1811320754716981</v>
+        <v>-0.08398268398268398</v>
       </c>
       <c r="H3">
-        <v>-0.2886792452830189</v>
+        <v>-0.2103896103896104</v>
       </c>
       <c r="I3">
-        <v>-0.4056603773584905</v>
+        <v>-0.4372294372294372</v>
       </c>
       <c r="J3">
-        <v>-0.4056603773584905</v>
+        <v>-0.4372294372294372</v>
       </c>
       <c r="K3">
-        <v>-0.392</v>
+        <v>-1.02</v>
       </c>
       <c r="L3">
-        <v>-0.369811320754717</v>
+        <v>-0.4415584415584415</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,58 +740,183 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="V3">
-        <v>0.04818481848184818</v>
+        <v>0.08472222222222221</v>
+      </c>
+      <c r="W3">
+        <v>-0.5483870967741935</v>
       </c>
       <c r="X3">
-        <v>0.06943301502953624</v>
+        <v>0.118190074035205</v>
+      </c>
+      <c r="Y3">
+        <v>-0.6665771708093986</v>
+      </c>
+      <c r="Z3">
+        <v>3.023560209424083</v>
+      </c>
+      <c r="AA3">
+        <v>-1.321989528795811</v>
       </c>
       <c r="AB3">
-        <v>0.06901348239604764</v>
+        <v>0.1166443065517569</v>
+      </c>
+      <c r="AC3">
+        <v>-1.438633835347568</v>
       </c>
       <c r="AD3">
-        <v>0.364</v>
+        <v>0.355</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.364</v>
+        <v>0.355</v>
       </c>
       <c r="AG3">
-        <v>-1.096</v>
+        <v>-0.865</v>
       </c>
       <c r="AH3">
-        <v>0.01187059744325593</v>
+        <v>0.0240596407997289</v>
       </c>
       <c r="AI3">
-        <v>0.1636690647482014</v>
+        <v>0.1033478893740902</v>
       </c>
       <c r="AJ3">
-        <v>-0.03752910560197233</v>
+        <v>-0.0639083856667898</v>
       </c>
       <c r="AK3">
-        <v>-1.43455497382199</v>
+        <v>-0.3905191873589165</v>
       </c>
       <c r="AL3">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AM3">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AN3">
-        <v>-0.8687350835322196</v>
+        <v>-0.369022869022869</v>
       </c>
       <c r="AO3">
-        <v>-35.83333333333333</v>
+        <v>-91.81818181818183</v>
       </c>
       <c r="AP3">
-        <v>2.615751789976134</v>
+        <v>0.8991683991683992</v>
       </c>
       <c r="AQ3">
-        <v>-35.83333333333333</v>
+        <v>-91.81818181818183</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Airobot Technologies AS (TLSE:AIR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Furn/Home Furnishings</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.1357798165137614</v>
+      </c>
+      <c r="H4">
+        <v>-0.1357798165137614</v>
+      </c>
+      <c r="I4">
+        <v>-0.1779816513761468</v>
+      </c>
+      <c r="J4">
+        <v>-0.1779816513761468</v>
+      </c>
+      <c r="K4">
+        <v>-0.099</v>
+      </c>
+      <c r="L4">
+        <v>-0.181651376146789</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.502</v>
+      </c>
+      <c r="V4">
+        <v>0.04735849056603774</v>
+      </c>
+      <c r="X4">
+        <v>0.1174948503382987</v>
+      </c>
+      <c r="AB4">
+        <v>0.1166489087930697</v>
+      </c>
+      <c r="AD4">
+        <v>0.143</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.143</v>
+      </c>
+      <c r="AG4">
+        <v>-0.359</v>
+      </c>
+      <c r="AH4">
+        <v>0.01331099320487759</v>
+      </c>
+      <c r="AI4">
+        <v>0.1986111111111111</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.03505517039351626</v>
+      </c>
+      <c r="AK4">
+        <v>-1.646788990825688</v>
+      </c>
+      <c r="AL4">
+        <v>0.002</v>
+      </c>
+      <c r="AM4">
+        <v>0.002</v>
+      </c>
+      <c r="AN4">
+        <v>-1.932432432432432</v>
+      </c>
+      <c r="AO4">
+        <v>-48.5</v>
+      </c>
+      <c r="AP4">
+        <v>4.851351351351352</v>
+      </c>
+      <c r="AQ4">
+        <v>-48.5</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/estonia/estonia_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_furn_home_furnishings.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.09387040280210159</v>
+        <v>-0.3637149028077754</v>
       </c>
       <c r="H2">
-        <v>-0.1961471103327495</v>
+        <v>-0.4416846652267818</v>
       </c>
       <c r="I2">
-        <v>-0.3877408056042032</v>
+        <v>-0.4170626349892009</v>
       </c>
       <c r="J2">
-        <v>-0.3877408056042032</v>
+        <v>-0.4170626349892009</v>
       </c>
       <c r="K2">
-        <v>-1.119</v>
+        <v>-1.947</v>
       </c>
       <c r="L2">
-        <v>-0.3919439579684764</v>
+        <v>-0.4205183585313175</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,61 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.722</v>
+        <v>0.622</v>
       </c>
       <c r="V2">
-        <v>0.06888</v>
+        <v>0.04449213161659513</v>
+      </c>
+      <c r="W2">
+        <v>-0.5815599045668369</v>
       </c>
       <c r="X2">
-        <v>0.1178424621867519</v>
+        <v>0.09284371415290497</v>
+      </c>
+      <c r="Y2">
+        <v>-0.6744036187197419</v>
       </c>
       <c r="Z2">
-        <v>3.736910994764397</v>
+        <v>1.932387312186978</v>
+      </c>
+      <c r="AA2">
+        <v>-1.209044152955746</v>
       </c>
       <c r="AB2">
-        <v>0.1166466076724133</v>
+        <v>0.09128045592449266</v>
+      </c>
+      <c r="AC2">
+        <v>-1.300324608880239</v>
       </c>
       <c r="AD2">
-        <v>0.498</v>
+        <v>0.491</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.498</v>
+        <v>0.491</v>
       </c>
       <c r="AG2">
-        <v>-1.224</v>
+        <v>-0.131</v>
       </c>
       <c r="AH2">
-        <v>0.01953094360341988</v>
+        <v>0.03392992882316357</v>
       </c>
       <c r="AI2">
-        <v>0.11985559566787</v>
+        <v>0.1307938199254129</v>
       </c>
       <c r="AJ2">
-        <v>-0.05148048452220727</v>
+        <v>-0.009459166726839482</v>
       </c>
       <c r="AK2">
-        <v>-0.5030826140567202</v>
+        <v>-0.04182630906768838</v>
       </c>
       <c r="AL2">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
       <c r="AM2">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
       <c r="AN2">
-        <v>-0.4806949806949807</v>
+        <v>-0.2706725468577729</v>
       </c>
       <c r="AO2">
-        <v>-85.15384615384616</v>
+        <v>-107.2777777777778</v>
       </c>
       <c r="AP2">
-        <v>1.181467181467181</v>
+        <v>0.07221609702315325</v>
       </c>
       <c r="AQ2">
-        <v>-85.15384615384616</v>
+        <v>-107.2777777777778</v>
       </c>
     </row>
     <row r="3">
@@ -701,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.08398268398268398</v>
+        <v>-0.3809384164222874</v>
       </c>
       <c r="H3">
-        <v>-0.2103896103896104</v>
+        <v>-0.4868035190615835</v>
       </c>
       <c r="I3">
-        <v>-0.4372294372294372</v>
+        <v>-0.4574780058651026</v>
       </c>
       <c r="J3">
-        <v>-0.4372294372294372</v>
+        <v>-0.4574780058651026</v>
       </c>
       <c r="K3">
-        <v>-1.02</v>
+        <v>-1.57</v>
       </c>
       <c r="L3">
-        <v>-0.4415584415584415</v>
+        <v>-0.4604105571847507</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.22</v>
+        <v>0.335</v>
       </c>
       <c r="V3">
-        <v>0.08472222222222221</v>
+        <v>0.03959810874704492</v>
       </c>
       <c r="W3">
-        <v>-0.5483870967741935</v>
+        <v>-0.5097402597402597</v>
       </c>
       <c r="X3">
-        <v>0.118190074035205</v>
+        <v>0.0931201635169569</v>
       </c>
       <c r="Y3">
-        <v>-0.6665771708093986</v>
+        <v>-0.6028604232572166</v>
       </c>
       <c r="Z3">
-        <v>3.023560209424083</v>
+        <v>1.565656565656566</v>
       </c>
       <c r="AA3">
-        <v>-1.321989528795811</v>
+        <v>-0.7162534435261708</v>
       </c>
       <c r="AB3">
-        <v>0.1166443065517569</v>
+        <v>0.09132662908339698</v>
       </c>
       <c r="AC3">
-        <v>-1.438633835347568</v>
+        <v>-0.8075800726095678</v>
       </c>
       <c r="AD3">
-        <v>0.355</v>
+        <v>0.341</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.355</v>
+        <v>0.341</v>
       </c>
       <c r="AG3">
-        <v>-0.865</v>
+        <v>0.006000000000000005</v>
       </c>
       <c r="AH3">
-        <v>0.0240596407997289</v>
+        <v>0.03874559709123963</v>
       </c>
       <c r="AI3">
-        <v>0.1033478893740902</v>
+        <v>0.1008577343981071</v>
       </c>
       <c r="AJ3">
-        <v>-0.0639083856667898</v>
+        <v>0.000708717221828491</v>
       </c>
       <c r="AK3">
-        <v>-0.3905191873589165</v>
+        <v>0.001969796454366384</v>
       </c>
       <c r="AL3">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="AM3">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="AN3">
-        <v>-0.369022869022869</v>
+        <v>-0.2319727891156463</v>
       </c>
       <c r="AO3">
-        <v>-91.81818181818183</v>
+        <v>-120</v>
       </c>
       <c r="AP3">
-        <v>0.8991683991683992</v>
+        <v>-0.004081632653061228</v>
       </c>
       <c r="AQ3">
-        <v>-91.81818181818183</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="4">
@@ -826,22 +838,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.1357798165137614</v>
+        <v>-0.3155737704918033</v>
       </c>
       <c r="H4">
-        <v>-0.1357798165137614</v>
+        <v>-0.3155737704918033</v>
       </c>
       <c r="I4">
-        <v>-0.1779816513761468</v>
+        <v>-0.3040983606557377</v>
       </c>
       <c r="J4">
-        <v>-0.1779816513761468</v>
+        <v>-0.3040983606557377</v>
       </c>
       <c r="K4">
-        <v>-0.099</v>
+        <v>-0.377</v>
       </c>
       <c r="L4">
-        <v>-0.181651376146789</v>
+        <v>-0.3090163934426229</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -865,58 +877,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.502</v>
+        <v>0.287</v>
       </c>
       <c r="V4">
-        <v>0.04735849056603774</v>
+        <v>0.05199275362318841</v>
+      </c>
+      <c r="W4">
+        <v>-0.6533795493934142</v>
       </c>
       <c r="X4">
-        <v>0.1174948503382987</v>
+        <v>0.09256726478885305</v>
+      </c>
+      <c r="Y4">
+        <v>-0.7459468141822673</v>
+      </c>
+      <c r="Z4">
+        <v>5.596330275229358</v>
+      </c>
+      <c r="AA4">
+        <v>-1.701834862385321</v>
       </c>
       <c r="AB4">
-        <v>0.1166489087930697</v>
+        <v>0.09123428276558833</v>
+      </c>
+      <c r="AC4">
+        <v>-1.79306914515091</v>
       </c>
       <c r="AD4">
-        <v>0.143</v>
+        <v>0.15</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.143</v>
+        <v>0.15</v>
       </c>
       <c r="AG4">
-        <v>-0.359</v>
+        <v>-0.137</v>
       </c>
       <c r="AH4">
-        <v>0.01331099320487759</v>
+        <v>0.02645502645502645</v>
       </c>
       <c r="AI4">
-        <v>0.1986111111111111</v>
+        <v>0.4021447721179625</v>
       </c>
       <c r="AJ4">
-        <v>-0.03505517039351626</v>
+        <v>-0.0254504922905443</v>
       </c>
       <c r="AK4">
-        <v>-1.646788990825688</v>
+        <v>-1.593023255813953</v>
       </c>
       <c r="AL4">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="AM4">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="AN4">
-        <v>-1.932432432432432</v>
+        <v>-0.436046511627907</v>
       </c>
       <c r="AO4">
-        <v>-48.5</v>
+        <v>-74.2</v>
       </c>
       <c r="AP4">
-        <v>4.851351351351352</v>
+        <v>0.3982558139534884</v>
       </c>
       <c r="AQ4">
-        <v>-48.5</v>
+        <v>-74.2</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/estonia/estonia_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_furn_home_furnishings.xlsx
@@ -1385,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1522,22 +1522,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09506134458824972</v>
+        <v>0.09490722189907322</v>
       </c>
       <c r="C2">
-        <v>5.330011456025169</v>
+        <v>5.292889903819746</v>
       </c>
       <c r="D2">
-        <v>5.209011456025168</v>
+        <v>5.225359903819746</v>
       </c>
       <c r="E2">
-        <v>-0.147</v>
+        <v>-0.09352999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.05347</v>
       </c>
       <c r="G2">
         <v>0.121</v>
@@ -1558,28 +1558,28 @@
         <v>0.143</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002689541</v>
       </c>
       <c r="N2">
-        <v>0.143</v>
+        <v>0.140310459</v>
       </c>
       <c r="O2">
-        <v>0.0286</v>
+        <v>0.02806209180000001</v>
       </c>
       <c r="P2">
-        <v>0.1144</v>
+        <v>0.1122483672</v>
       </c>
       <c r="Q2">
-        <v>0.1714</v>
+        <v>0.1692483672</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09506134458824972</v>
+        <v>0.09545941605966993</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460947</v>
+        <v>0.9420207723624269</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>53.16892361930903</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1604,22 +1604,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09490722189907322</v>
+        <v>0.09475309920989672</v>
       </c>
       <c r="C3">
-        <v>5.292889903819746</v>
+        <v>5.25587129368658</v>
       </c>
       <c r="D3">
-        <v>5.225359903819746</v>
+        <v>5.241811293686579</v>
       </c>
       <c r="E3">
-        <v>-0.09352999999999999</v>
+        <v>-0.04005999999999998</v>
       </c>
       <c r="F3">
-        <v>0.05347</v>
+        <v>0.10694</v>
       </c>
       <c r="G3">
         <v>0.121</v>
@@ -1640,28 +1640,28 @@
         <v>0.143</v>
       </c>
       <c r="M3">
-        <v>0.002689541</v>
+        <v>0.005379082</v>
       </c>
       <c r="N3">
-        <v>0.140310459</v>
+        <v>0.137620918</v>
       </c>
       <c r="O3">
-        <v>0.02806209180000001</v>
+        <v>0.0275241836</v>
       </c>
       <c r="P3">
-        <v>0.1122483672</v>
+        <v>0.1100967344</v>
       </c>
       <c r="Q3">
-        <v>0.1692483672</v>
+        <v>0.1670967344</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09545941605966993</v>
+        <v>0.09586561143867013</v>
       </c>
       <c r="T3">
-        <v>0.9420207723624269</v>
+        <v>0.949726148603582</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>53.16892361930903</v>
+        <v>26.58446180965451</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1686,22 +1686,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09475309920989672</v>
+        <v>0.09459897652072023</v>
       </c>
       <c r="C4">
-        <v>5.25587129368658</v>
+        <v>5.218956600997084</v>
       </c>
       <c r="D4">
-        <v>5.241811293686579</v>
+        <v>5.258366600997085</v>
       </c>
       <c r="E4">
-        <v>-0.04005999999999998</v>
+        <v>0.01341000000000001</v>
       </c>
       <c r="F4">
-        <v>0.10694</v>
+        <v>0.16041</v>
       </c>
       <c r="G4">
         <v>0.121</v>
@@ -1722,28 +1722,28 @@
         <v>0.143</v>
       </c>
       <c r="M4">
-        <v>0.005379082</v>
+        <v>0.008068622999999999</v>
       </c>
       <c r="N4">
-        <v>0.137620918</v>
+        <v>0.134931377</v>
       </c>
       <c r="O4">
-        <v>0.0275241836</v>
+        <v>0.02698627540000001</v>
       </c>
       <c r="P4">
-        <v>0.1100967344</v>
+        <v>0.1079451016</v>
       </c>
       <c r="Q4">
-        <v>0.1670967344</v>
+        <v>0.1649451016</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09586561143867013</v>
+        <v>0.09628018198012395</v>
       </c>
       <c r="T4">
-        <v>0.949726148603582</v>
+        <v>0.9575903985816681</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>26.58446180965451</v>
+        <v>17.72297453976968</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1768,22 +1768,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09459897652072023</v>
+        <v>0.09444485383154373</v>
       </c>
       <c r="C5">
-        <v>5.218956600997084</v>
+        <v>5.182146813483859</v>
       </c>
       <c r="D5">
-        <v>5.258366600997085</v>
+        <v>5.275026813483858</v>
       </c>
       <c r="E5">
-        <v>0.01341000000000001</v>
+        <v>0.06688000000000002</v>
       </c>
       <c r="F5">
-        <v>0.16041</v>
+        <v>0.21388</v>
       </c>
       <c r="G5">
         <v>0.121</v>
@@ -1804,28 +1804,28 @@
         <v>0.143</v>
       </c>
       <c r="M5">
-        <v>0.008068622999999999</v>
+        <v>0.010758164</v>
       </c>
       <c r="N5">
-        <v>0.134931377</v>
+        <v>0.132241836</v>
       </c>
       <c r="O5">
-        <v>0.02698627540000001</v>
+        <v>0.0264483672</v>
       </c>
       <c r="P5">
-        <v>0.1079451016</v>
+        <v>0.1057934688</v>
       </c>
       <c r="Q5">
-        <v>0.1649451016</v>
+        <v>0.1627934688</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09628018198012395</v>
+        <v>0.09670338940785805</v>
       </c>
       <c r="T5">
-        <v>0.9575903985816681</v>
+        <v>0.9656184871009647</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>17.72297453976968</v>
+        <v>13.29223090482725</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1850,22 +1850,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09444485383154373</v>
+        <v>0.09435073114236722</v>
       </c>
       <c r="C6">
-        <v>5.182146813483859</v>
+        <v>5.138903224033832</v>
       </c>
       <c r="D6">
-        <v>5.275026813483858</v>
+        <v>5.285253224033833</v>
       </c>
       <c r="E6">
-        <v>0.06688000000000002</v>
+        <v>0.12035</v>
       </c>
       <c r="F6">
-        <v>0.21388</v>
+        <v>0.26735</v>
       </c>
       <c r="G6">
         <v>0.121</v>
@@ -1886,45 +1886,45 @@
         <v>0.143</v>
       </c>
       <c r="M6">
-        <v>0.010758164</v>
+        <v>0.01384873</v>
       </c>
       <c r="N6">
-        <v>0.132241836</v>
+        <v>0.12915127</v>
       </c>
       <c r="O6">
-        <v>0.0264483672</v>
+        <v>0.025830254</v>
       </c>
       <c r="P6">
-        <v>0.1057934688</v>
+        <v>0.103321016</v>
       </c>
       <c r="Q6">
-        <v>0.1627934688</v>
+        <v>0.160321016</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09670338940785805</v>
+        <v>0.09713550646564971</v>
       </c>
       <c r="T6">
-        <v>0.9656184871009647</v>
+        <v>0.9738155880101407</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.29223090482725</v>
+        <v>10.32585659479245</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1932,22 +1932,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09435073114236722</v>
+        <v>0.09429020845319072</v>
       </c>
       <c r="C7">
-        <v>5.138903224033832</v>
+        <v>5.092029973115786</v>
       </c>
       <c r="D7">
-        <v>5.285253224033833</v>
+        <v>5.291849973115786</v>
       </c>
       <c r="E7">
-        <v>0.12035</v>
+        <v>0.1738200000000001</v>
       </c>
       <c r="F7">
-        <v>0.26735</v>
+        <v>0.32082</v>
       </c>
       <c r="G7">
         <v>0.121</v>
@@ -1968,45 +1968,45 @@
         <v>0.143</v>
       </c>
       <c r="M7">
-        <v>0.01384873</v>
+        <v>0.01716387</v>
       </c>
       <c r="N7">
-        <v>0.12915127</v>
+        <v>0.12583613</v>
       </c>
       <c r="O7">
-        <v>0.025830254</v>
+        <v>0.025167226</v>
       </c>
       <c r="P7">
-        <v>0.103321016</v>
+        <v>0.100668904</v>
       </c>
       <c r="Q7">
-        <v>0.160321016</v>
+        <v>0.157668904</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09713550646564971</v>
+        <v>0.09757681750339439</v>
       </c>
       <c r="T7">
-        <v>0.9738155880101407</v>
+        <v>0.9821870953216401</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.32585659479245</v>
+        <v>8.331454386452474</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2014,22 +2014,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09429020845319072</v>
+        <v>0.09420648576401423</v>
       </c>
       <c r="C8">
-        <v>5.092029973115786</v>
+        <v>5.047712629076553</v>
       </c>
       <c r="D8">
-        <v>5.291849973115786</v>
+        <v>5.301002629076553</v>
       </c>
       <c r="E8">
-        <v>0.17382</v>
+        <v>0.22729</v>
       </c>
       <c r="F8">
-        <v>0.32082</v>
+        <v>0.37429</v>
       </c>
       <c r="G8">
         <v>0.121</v>
@@ -2050,45 +2050,45 @@
         <v>0.143</v>
       </c>
       <c r="M8">
-        <v>0.01716387</v>
+        <v>0.020323947</v>
       </c>
       <c r="N8">
-        <v>0.12583613</v>
+        <v>0.122676053</v>
       </c>
       <c r="O8">
-        <v>0.025167226</v>
+        <v>0.0245352106</v>
       </c>
       <c r="P8">
-        <v>0.100668904</v>
+        <v>0.09814084240000001</v>
       </c>
       <c r="Q8">
-        <v>0.157668904</v>
+        <v>0.1551408424</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09757681750339439</v>
+        <v>0.09802761910109058</v>
       </c>
       <c r="T8">
-        <v>0.9821870953216401</v>
+        <v>0.9907386350484403</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.331454386452474</v>
+        <v>7.036034880429475</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2096,22 +2096,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09420648576401423</v>
+        <v>0.09408436307483774</v>
       </c>
       <c r="C9">
-        <v>5.047712629076553</v>
+        <v>5.007650131115901</v>
       </c>
       <c r="D9">
-        <v>5.301002629076553</v>
+        <v>5.314410131115901</v>
       </c>
       <c r="E9">
-        <v>0.2272900000000001</v>
+        <v>0.28076</v>
       </c>
       <c r="F9">
-        <v>0.3742900000000001</v>
+        <v>0.42776</v>
       </c>
       <c r="G9">
         <v>0.121</v>
@@ -2132,28 +2132,28 @@
         <v>0.143</v>
       </c>
       <c r="M9">
-        <v>0.02032394700000001</v>
+        <v>0.023227368</v>
       </c>
       <c r="N9">
-        <v>0.122676053</v>
+        <v>0.119772632</v>
       </c>
       <c r="O9">
-        <v>0.0245352106</v>
+        <v>0.02395452640000001</v>
       </c>
       <c r="P9">
-        <v>0.09814084240000001</v>
+        <v>0.09581810560000001</v>
       </c>
       <c r="Q9">
-        <v>0.1551408424</v>
+        <v>0.1528181056</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09802761910109058</v>
+        <v>0.09848822073351927</v>
       </c>
       <c r="T9">
-        <v>0.9907386350484403</v>
+        <v>0.9994760778127796</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>7.036034880429474</v>
+        <v>6.156530520375791</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2178,22 +2178,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09408436307483774</v>
+        <v>0.09403424038566123</v>
       </c>
       <c r="C10">
-        <v>5.007650131115901</v>
+        <v>4.959702609028449</v>
       </c>
       <c r="D10">
-        <v>5.314410131115901</v>
+        <v>5.31993260902845</v>
       </c>
       <c r="E10">
-        <v>0.28076</v>
+        <v>0.33423</v>
       </c>
       <c r="F10">
-        <v>0.42776</v>
+        <v>0.48123</v>
       </c>
       <c r="G10">
         <v>0.121</v>
@@ -2214,45 +2214,45 @@
         <v>0.143</v>
       </c>
       <c r="M10">
-        <v>0.023227368</v>
+        <v>0.026612019</v>
       </c>
       <c r="N10">
-        <v>0.119772632</v>
+        <v>0.116387981</v>
       </c>
       <c r="O10">
-        <v>0.02395452640000001</v>
+        <v>0.0232775962</v>
       </c>
       <c r="P10">
-        <v>0.09581810560000001</v>
+        <v>0.09311038480000002</v>
       </c>
       <c r="Q10">
-        <v>0.1528181056</v>
+        <v>0.1501103848</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09848822073351927</v>
+        <v>0.0989589454787486</v>
       </c>
       <c r="T10">
-        <v>0.9994760778127796</v>
+        <v>1.008405552286225</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>6.156530520375791</v>
+        <v>5.373511870707743</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2260,22 +2260,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09403424038566123</v>
+        <v>0.09392011769648473</v>
       </c>
       <c r="C11">
-        <v>4.959702609028449</v>
+        <v>4.91884947375454</v>
       </c>
       <c r="D11">
-        <v>5.31993260902845</v>
+        <v>5.332549473754541</v>
       </c>
       <c r="E11">
-        <v>0.33423</v>
+        <v>0.3876999999999999</v>
       </c>
       <c r="F11">
-        <v>0.48123</v>
+        <v>0.5347</v>
       </c>
       <c r="G11">
         <v>0.121</v>
@@ -2296,28 +2296,28 @@
         <v>0.143</v>
       </c>
       <c r="M11">
-        <v>0.026612019</v>
+        <v>0.02956891</v>
       </c>
       <c r="N11">
-        <v>0.116387981</v>
+        <v>0.11343109</v>
       </c>
       <c r="O11">
-        <v>0.0232775962</v>
+        <v>0.022686218</v>
       </c>
       <c r="P11">
-        <v>0.09311038480000002</v>
+        <v>0.090744872</v>
       </c>
       <c r="Q11">
-        <v>0.1501103848</v>
+        <v>0.147744872</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0989589454787486</v>
+        <v>0.09944013077387193</v>
       </c>
       <c r="T11">
-        <v>1.008405552286225</v>
+        <v>1.017533459525747</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.373511870707743</v>
+        <v>4.83616068363697</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2342,22 +2342,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09392011769648473</v>
+        <v>0.09402599500730824</v>
       </c>
       <c r="C12">
-        <v>4.91884947375454</v>
+        <v>4.853672177761396</v>
       </c>
       <c r="D12">
-        <v>5.332549473754541</v>
+        <v>5.320842177761396</v>
       </c>
       <c r="E12">
-        <v>0.3877</v>
+        <v>0.4411700000000001</v>
       </c>
       <c r="F12">
-        <v>0.5347000000000001</v>
+        <v>0.5881700000000001</v>
       </c>
       <c r="G12">
         <v>0.121</v>
@@ -2378,45 +2378,45 @@
         <v>0.143</v>
       </c>
       <c r="M12">
-        <v>0.02956891</v>
+        <v>0.033996226</v>
       </c>
       <c r="N12">
-        <v>0.11343109</v>
+        <v>0.109003774</v>
       </c>
       <c r="O12">
-        <v>0.022686218</v>
+        <v>0.0218007548</v>
       </c>
       <c r="P12">
-        <v>0.090744872</v>
+        <v>0.08720301920000001</v>
       </c>
       <c r="Q12">
-        <v>0.147744872</v>
+        <v>0.1442030192</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09944013077387193</v>
+        <v>0.09993212922169464</v>
       </c>
       <c r="T12">
-        <v>1.017533459525748</v>
+        <v>1.02686648827627</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.836160683636969</v>
+        <v>4.206349257708782</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09402599500730824</v>
+        <v>0.09426787231813173</v>
       </c>
       <c r="C13">
-        <v>4.853672177761396</v>
+        <v>4.773648691179075</v>
       </c>
       <c r="D13">
-        <v>5.320842177761396</v>
+        <v>5.294288691179075</v>
       </c>
       <c r="E13">
-        <v>0.4411700000000001</v>
+        <v>0.49464</v>
       </c>
       <c r="F13">
-        <v>0.5881700000000001</v>
+        <v>0.64164</v>
       </c>
       <c r="G13">
         <v>0.121</v>
@@ -2460,45 +2460,45 @@
         <v>0.143</v>
       </c>
       <c r="M13">
-        <v>0.033996226</v>
+        <v>0.039332532</v>
       </c>
       <c r="N13">
-        <v>0.109003774</v>
+        <v>0.103667468</v>
       </c>
       <c r="O13">
-        <v>0.0218007548</v>
+        <v>0.0207334936</v>
       </c>
       <c r="P13">
-        <v>0.08720301920000001</v>
+        <v>0.08293397440000001</v>
       </c>
       <c r="Q13">
-        <v>0.1442030192</v>
+        <v>0.1399339744</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09993212922169464</v>
+        <v>0.1004353094524224</v>
       </c>
       <c r="T13">
-        <v>1.02686648827627</v>
+        <v>1.036411631316578</v>
       </c>
       <c r="U13">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.206349257708782</v>
+        <v>3.635667289357319</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2506,22 +2506,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09426787231813173</v>
+        <v>0.09449294962895524</v>
       </c>
       <c r="C14">
-        <v>4.773648691179075</v>
+        <v>4.695706477636577</v>
       </c>
       <c r="D14">
-        <v>5.294288691179075</v>
+        <v>5.269816477636576</v>
       </c>
       <c r="E14">
-        <v>0.49464</v>
+        <v>0.5481100000000001</v>
       </c>
       <c r="F14">
-        <v>0.64164</v>
+        <v>0.6951100000000001</v>
       </c>
       <c r="G14">
         <v>0.121</v>
@@ -2542,45 +2542,45 @@
         <v>0.143</v>
       </c>
       <c r="M14">
-        <v>0.039332532</v>
+        <v>0.04455655100000001</v>
       </c>
       <c r="N14">
-        <v>0.103667468</v>
+        <v>0.098443449</v>
       </c>
       <c r="O14">
-        <v>0.0207334936</v>
+        <v>0.0196886898</v>
       </c>
       <c r="P14">
-        <v>0.08293397440000001</v>
+        <v>0.0787547592</v>
       </c>
       <c r="Q14">
-        <v>0.1399339744</v>
+        <v>0.1357547592</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1004353094524224</v>
+        <v>0.1009500570447761</v>
       </c>
       <c r="T14">
-        <v>1.036411631316578</v>
+        <v>1.046176202932524</v>
       </c>
       <c r="U14">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.635667289357319</v>
+        <v>3.209404605845726</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2588,22 +2588,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09449294962895524</v>
+        <v>0.09532282693977874</v>
       </c>
       <c r="C15">
-        <v>4.695706477636577</v>
+        <v>4.553927683546279</v>
       </c>
       <c r="D15">
-        <v>5.269816477636576</v>
+        <v>5.181507683546279</v>
       </c>
       <c r="E15">
-        <v>0.5481100000000001</v>
+        <v>0.6015800000000001</v>
       </c>
       <c r="F15">
-        <v>0.6951100000000001</v>
+        <v>0.7485800000000001</v>
       </c>
       <c r="G15">
         <v>0.121</v>
@@ -2624,45 +2624,45 @@
         <v>0.143</v>
       </c>
       <c r="M15">
-        <v>0.04455655100000001</v>
+        <v>0.05382290200000001</v>
       </c>
       <c r="N15">
-        <v>0.098443449</v>
+        <v>0.08917709800000001</v>
       </c>
       <c r="O15">
-        <v>0.0196886898</v>
+        <v>0.0178354196</v>
       </c>
       <c r="P15">
-        <v>0.0787547592</v>
+        <v>0.07134167840000001</v>
       </c>
       <c r="Q15">
-        <v>0.1357547592</v>
+        <v>0.1283416784</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1009500570447761</v>
+        <v>0.1014767755113706</v>
       </c>
       <c r="T15">
-        <v>1.046176202932524</v>
+        <v>1.056167857609307</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.209404605845726</v>
+        <v>2.656861571678168</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2670,22 +2670,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09532282693977874</v>
+        <v>0.09580950425060224</v>
       </c>
       <c r="C16">
-        <v>4.553927683546279</v>
+        <v>4.450032824047512</v>
       </c>
       <c r="D16">
-        <v>5.181507683546279</v>
+        <v>5.131082824047512</v>
       </c>
       <c r="E16">
-        <v>0.6015800000000001</v>
+        <v>0.6550500000000001</v>
       </c>
       <c r="F16">
-        <v>0.7485800000000001</v>
+        <v>0.8020500000000002</v>
       </c>
       <c r="G16">
         <v>0.121</v>
@@ -2706,45 +2706,45 @@
         <v>0.143</v>
       </c>
       <c r="M16">
-        <v>0.05382290200000001</v>
+        <v>0.06079539000000002</v>
       </c>
       <c r="N16">
-        <v>0.08917709800000001</v>
+        <v>0.08220461</v>
       </c>
       <c r="O16">
-        <v>0.0178354196</v>
+        <v>0.016440922</v>
       </c>
       <c r="P16">
-        <v>0.07134167840000001</v>
+        <v>0.065763688</v>
       </c>
       <c r="Q16">
-        <v>0.1283416784</v>
+        <v>0.122763688</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1014767755113706</v>
+        <v>0.1020158873536497</v>
       </c>
       <c r="T16">
-        <v>1.056167857609307</v>
+        <v>1.06639461004319</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.656861571678168</v>
+        <v>2.352152029948323</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2752,22 +2752,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09580950425060222</v>
+        <v>0.09585938156142573</v>
       </c>
       <c r="C17">
-        <v>4.450032824047514</v>
+        <v>4.391450403460333</v>
       </c>
       <c r="D17">
-        <v>5.131082824047514</v>
+        <v>5.125970403460332</v>
       </c>
       <c r="E17">
-        <v>0.65505</v>
+        <v>0.70852</v>
       </c>
       <c r="F17">
-        <v>0.80205</v>
+        <v>0.8555200000000001</v>
       </c>
       <c r="G17">
         <v>0.121</v>
@@ -2788,28 +2788,28 @@
         <v>0.143</v>
       </c>
       <c r="M17">
-        <v>0.06079539</v>
+        <v>0.06484841600000001</v>
       </c>
       <c r="N17">
-        <v>0.08220461000000001</v>
+        <v>0.07815158400000001</v>
       </c>
       <c r="O17">
-        <v>0.016440922</v>
+        <v>0.0156303168</v>
       </c>
       <c r="P17">
-        <v>0.06576368800000001</v>
+        <v>0.06252126720000001</v>
       </c>
       <c r="Q17">
-        <v>0.122763688</v>
+        <v>0.1195212672</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1020158873536497</v>
+        <v>0.1025678351921735</v>
       </c>
       <c r="T17">
-        <v>1.06639461004319</v>
+        <v>1.076864856582642</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.352152029948323</v>
+        <v>2.205142528076554</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2834,22 +2834,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09585938156142573</v>
+        <v>0.09590925887224924</v>
       </c>
       <c r="C18">
-        <v>4.391450403460333</v>
+        <v>4.332878160385108</v>
       </c>
       <c r="D18">
-        <v>5.125970403460332</v>
+        <v>5.120868160385109</v>
       </c>
       <c r="E18">
-        <v>0.70852</v>
+        <v>0.7619900000000002</v>
       </c>
       <c r="F18">
-        <v>0.8555200000000001</v>
+        <v>0.9089900000000002</v>
       </c>
       <c r="G18">
         <v>0.121</v>
@@ -2870,28 +2870,28 @@
         <v>0.143</v>
       </c>
       <c r="M18">
-        <v>0.06484841600000001</v>
+        <v>0.06890144200000002</v>
       </c>
       <c r="N18">
-        <v>0.07815158400000001</v>
+        <v>0.07409855799999999</v>
       </c>
       <c r="O18">
-        <v>0.0156303168</v>
+        <v>0.0148197116</v>
       </c>
       <c r="P18">
-        <v>0.06252126720000001</v>
+        <v>0.05927884639999999</v>
       </c>
       <c r="Q18">
-        <v>0.1195212672</v>
+        <v>0.1162788464</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1025678351921735</v>
+        <v>0.1031330829786135</v>
       </c>
       <c r="T18">
-        <v>1.076864856582642</v>
+        <v>1.087587398219431</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.205142528076554</v>
+        <v>2.075428261719108</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2916,22 +2916,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09590925887224924</v>
+        <v>0.09800393618307274</v>
       </c>
       <c r="C19">
-        <v>4.332878160385108</v>
+        <v>4.073933877571253</v>
       </c>
       <c r="D19">
-        <v>5.120868160385109</v>
+        <v>4.915393877571254</v>
       </c>
       <c r="E19">
-        <v>0.7619900000000002</v>
+        <v>0.8154600000000002</v>
       </c>
       <c r="F19">
-        <v>0.9089900000000002</v>
+        <v>0.9624600000000002</v>
       </c>
       <c r="G19">
         <v>0.121</v>
@@ -2952,45 +2952,45 @@
         <v>0.143</v>
       </c>
       <c r="M19">
-        <v>0.06890144200000002</v>
+        <v>0.08662140000000002</v>
       </c>
       <c r="N19">
-        <v>0.07409855799999999</v>
+        <v>0.0563786</v>
       </c>
       <c r="O19">
-        <v>0.0148197116</v>
+        <v>0.01127572</v>
       </c>
       <c r="P19">
-        <v>0.05927884639999999</v>
+        <v>0.04510288</v>
       </c>
       <c r="Q19">
-        <v>0.1162788464</v>
+        <v>0.10210288</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1031330829786135</v>
+        <v>0.1037121172964302</v>
       </c>
       <c r="T19">
-        <v>1.087587398219431</v>
+        <v>1.098571465261994</v>
       </c>
       <c r="U19">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.075428261719108</v>
+        <v>1.650862258056323</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2998,22 +2998,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09800393618307274</v>
+        <v>0.09816741349389625</v>
       </c>
       <c r="C20">
-        <v>4.073933877571253</v>
+        <v>4.005119308895213</v>
       </c>
       <c r="D20">
-        <v>4.915393877571254</v>
+        <v>4.900049308895214</v>
       </c>
       <c r="E20">
-        <v>0.8154600000000001</v>
+        <v>0.86893</v>
       </c>
       <c r="F20">
-        <v>0.9624600000000001</v>
+        <v>1.01593</v>
       </c>
       <c r="G20">
         <v>0.121</v>
@@ -3034,28 +3034,28 @@
         <v>0.143</v>
       </c>
       <c r="M20">
-        <v>0.0866214</v>
+        <v>0.09143369999999999</v>
       </c>
       <c r="N20">
-        <v>0.05637860000000001</v>
+        <v>0.05156630000000002</v>
       </c>
       <c r="O20">
-        <v>0.01127572</v>
+        <v>0.01031326</v>
       </c>
       <c r="P20">
-        <v>0.04510288000000001</v>
+        <v>0.04125304000000002</v>
       </c>
       <c r="Q20">
-        <v>0.10210288</v>
+        <v>0.09825304000000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1037121172964302</v>
+        <v>0.1043054487578966</v>
       </c>
       <c r="T20">
-        <v>1.098571465261994</v>
+        <v>1.109826743836473</v>
       </c>
       <c r="U20">
         <v>0.09</v>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>1.650862258056323</v>
+        <v>1.563974770790201</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3080,22 +3080,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09816741349389625</v>
+        <v>0.1081176682401283</v>
       </c>
       <c r="C21">
-        <v>4.005119308895213</v>
+        <v>3.169259013020673</v>
       </c>
       <c r="D21">
-        <v>4.900049308895214</v>
+        <v>4.117659013020672</v>
       </c>
       <c r="E21">
-        <v>0.86893</v>
+        <v>0.9224000000000001</v>
       </c>
       <c r="F21">
-        <v>1.01593</v>
+        <v>1.0694</v>
       </c>
       <c r="G21">
         <v>0.121</v>
@@ -3116,45 +3116,45 @@
         <v>0.143</v>
       </c>
       <c r="M21">
-        <v>0.09143369999999999</v>
+        <v>0.15698792</v>
       </c>
       <c r="N21">
-        <v>0.05156630000000002</v>
+        <v>-0.01398792000000001</v>
       </c>
       <c r="O21">
-        <v>0.01031326</v>
+        <v>-0.002797584000000003</v>
       </c>
       <c r="P21">
-        <v>0.04125304000000002</v>
+        <v>-0.01119033600000001</v>
       </c>
       <c r="Q21">
-        <v>0.09825304000000001</v>
+        <v>0.04580966399999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1043054487578966</v>
+        <v>0.1051330774452884</v>
       </c>
       <c r="T21">
-        <v>1.109826743836473</v>
+        <v>1.125526554208575</v>
       </c>
       <c r="U21">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.2</v>
+        <v>0.1821796224830547</v>
       </c>
       <c r="W21">
-        <v>0.07199999999999999</v>
+        <v>0.1200560314194876</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.563974770790201</v>
+        <v>0.9108981124152736</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3162,22 +3162,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1081176682401283</v>
+        <v>0.1091276682401282</v>
       </c>
       <c r="C22">
-        <v>3.169259013020673</v>
+        <v>3.050117313450411</v>
       </c>
       <c r="D22">
-        <v>4.117659013020672</v>
+        <v>4.051987313450412</v>
       </c>
       <c r="E22">
-        <v>0.9224000000000001</v>
+        <v>0.9758700000000002</v>
       </c>
       <c r="F22">
-        <v>1.0694</v>
+        <v>1.12287</v>
       </c>
       <c r="G22">
         <v>0.121</v>
@@ -3198,37 +3198,37 @@
         <v>0.143</v>
       </c>
       <c r="M22">
-        <v>0.15698792</v>
+        <v>0.1648373160000001</v>
       </c>
       <c r="N22">
-        <v>-0.01398792000000001</v>
+        <v>-0.02183731600000005</v>
       </c>
       <c r="O22">
-        <v>-0.002797584000000003</v>
+        <v>-0.004367463200000011</v>
       </c>
       <c r="P22">
-        <v>-0.01119033600000001</v>
+        <v>-0.01746985280000004</v>
       </c>
       <c r="Q22">
-        <v>0.04580966399999999</v>
+        <v>0.03953014719999996</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1051330774452884</v>
+        <v>0.1058841290585199</v>
       </c>
       <c r="T22">
-        <v>1.125526554208575</v>
+        <v>1.139773725780836</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.1821796224830547</v>
+        <v>0.173504402364814</v>
       </c>
       <c r="W22">
-        <v>0.1200560314194876</v>
+        <v>0.1213295537328453</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.9108981124152736</v>
+        <v>0.86752201182407</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3244,22 +3244,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1091276682401282</v>
+        <v>0.1101376682401283</v>
       </c>
       <c r="C23">
-        <v>3.050117313450412</v>
+        <v>2.933037498259247</v>
       </c>
       <c r="D23">
-        <v>4.051987313450412</v>
+        <v>3.988377498259247</v>
       </c>
       <c r="E23">
-        <v>0.97587</v>
+        <v>1.02934</v>
       </c>
       <c r="F23">
-        <v>1.12287</v>
+        <v>1.17634</v>
       </c>
       <c r="G23">
         <v>0.121</v>
@@ -3280,37 +3280,37 @@
         <v>0.143</v>
       </c>
       <c r="M23">
-        <v>0.164837316</v>
+        <v>0.172686712</v>
       </c>
       <c r="N23">
-        <v>-0.021837316</v>
+        <v>-0.02968671200000003</v>
       </c>
       <c r="O23">
-        <v>-0.004367463199999999</v>
+        <v>-0.005937342400000007</v>
       </c>
       <c r="P23">
-        <v>-0.0174698528</v>
+        <v>-0.02374936960000002</v>
       </c>
       <c r="Q23">
-        <v>0.0395301472</v>
+        <v>0.03325063039999998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1058841290585199</v>
+        <v>0.106654438405424</v>
       </c>
       <c r="T23">
-        <v>1.139773725780836</v>
+        <v>1.154386209444693</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.1735044023648141</v>
+        <v>0.1656178386209588</v>
       </c>
       <c r="W23">
-        <v>0.1213295537328453</v>
+        <v>0.1224873012904433</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8675220118240703</v>
+        <v>0.8280891931047942</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3326,22 +3326,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1101376682401283</v>
+        <v>0.1240503558005318</v>
       </c>
       <c r="C24">
-        <v>2.933037498259247</v>
+        <v>2.170445482920787</v>
       </c>
       <c r="D24">
-        <v>3.988377498259247</v>
+        <v>3.279255482920787</v>
       </c>
       <c r="E24">
-        <v>1.02934</v>
+        <v>1.08281</v>
       </c>
       <c r="F24">
-        <v>1.17634</v>
+        <v>1.22981</v>
       </c>
       <c r="G24">
         <v>0.121</v>
@@ -3362,45 +3362,45 @@
         <v>0.143</v>
       </c>
       <c r="M24">
-        <v>0.172686712</v>
+        <v>0.246945848</v>
       </c>
       <c r="N24">
-        <v>-0.02968671200000003</v>
+        <v>-0.103945848</v>
       </c>
       <c r="O24">
-        <v>-0.005937342400000007</v>
+        <v>-0.0207891696</v>
       </c>
       <c r="P24">
-        <v>-0.02374936960000002</v>
+        <v>-0.0831566784</v>
       </c>
       <c r="Q24">
-        <v>0.03325063039999998</v>
+        <v>-0.0261566784</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.106654438405424</v>
+        <v>0.1080716227488756</v>
       </c>
       <c r="T24">
-        <v>1.154386209444693</v>
+        <v>1.181269672757956</v>
       </c>
       <c r="U24">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1656178386209588</v>
+        <v>0.115814864803882</v>
       </c>
       <c r="W24">
-        <v>0.1224873012904433</v>
+        <v>0.1775443751473805</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.8280891931047942</v>
+        <v>0.5790743240194101</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3408,22 +3408,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1240503558005318</v>
+        <v>0.1256003558005318</v>
       </c>
       <c r="C25">
-        <v>2.170445482920787</v>
+        <v>2.053280954900983</v>
       </c>
       <c r="D25">
-        <v>3.279255482920787</v>
+        <v>3.215560954900983</v>
       </c>
       <c r="E25">
-        <v>1.08281</v>
+        <v>1.13628</v>
       </c>
       <c r="F25">
-        <v>1.22981</v>
+        <v>1.28328</v>
       </c>
       <c r="G25">
         <v>0.121</v>
@@ -3444,37 +3444,37 @@
         <v>0.143</v>
       </c>
       <c r="M25">
-        <v>0.246945848</v>
+        <v>0.257682624</v>
       </c>
       <c r="N25">
-        <v>-0.103945848</v>
+        <v>-0.114682624</v>
       </c>
       <c r="O25">
-        <v>-0.0207891696</v>
+        <v>-0.0229365248</v>
       </c>
       <c r="P25">
-        <v>-0.0831566784</v>
+        <v>-0.09174609920000001</v>
       </c>
       <c r="Q25">
-        <v>-0.0261566784</v>
+        <v>-0.03474609920000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1080716227488756</v>
+        <v>0.1088909862060977</v>
       </c>
       <c r="T25">
-        <v>1.181269672757956</v>
+        <v>1.196812694767929</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.115814864803882</v>
+        <v>0.1109892454370536</v>
       </c>
       <c r="W25">
-        <v>0.1775443751473805</v>
+        <v>0.1785133595162396</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5790743240194101</v>
+        <v>0.5549462271852681</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3490,22 +3490,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1256003558005317</v>
+        <v>0.1271503558005317</v>
       </c>
       <c r="C26">
-        <v>2.053280954900985</v>
+        <v>1.938543620160403</v>
       </c>
       <c r="D26">
-        <v>3.215560954900984</v>
+        <v>3.154293620160403</v>
       </c>
       <c r="E26">
-        <v>1.13628</v>
+        <v>1.18975</v>
       </c>
       <c r="F26">
-        <v>1.28328</v>
+        <v>1.33675</v>
       </c>
       <c r="G26">
         <v>0.121</v>
@@ -3526,37 +3526,37 @@
         <v>0.143</v>
       </c>
       <c r="M26">
-        <v>0.257682624</v>
+        <v>0.2684194</v>
       </c>
       <c r="N26">
-        <v>-0.114682624</v>
+        <v>-0.1254194</v>
       </c>
       <c r="O26">
-        <v>-0.0229365248</v>
+        <v>-0.02508388</v>
       </c>
       <c r="P26">
-        <v>-0.09174609920000001</v>
+        <v>-0.10033552</v>
       </c>
       <c r="Q26">
-        <v>-0.03474609920000001</v>
+        <v>-0.04333552000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1088909862060977</v>
+        <v>0.1097321993555123</v>
       </c>
       <c r="T26">
-        <v>1.196812694767929</v>
+        <v>1.212770197364835</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1109892454370536</v>
+        <v>0.1065496756195715</v>
       </c>
       <c r="W26">
-        <v>0.1785133595162396</v>
+        <v>0.1794048251355901</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5549462271852681</v>
+        <v>0.5327483780978572</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3572,22 +3572,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1271503558005317</v>
+        <v>0.1287003558005317</v>
       </c>
       <c r="C27">
-        <v>1.938543620160403</v>
+        <v>1.826097333942616</v>
       </c>
       <c r="D27">
-        <v>3.154293620160403</v>
+        <v>3.095317333942616</v>
       </c>
       <c r="E27">
-        <v>1.18975</v>
+        <v>1.24322</v>
       </c>
       <c r="F27">
-        <v>1.33675</v>
+        <v>1.39022</v>
       </c>
       <c r="G27">
         <v>0.121</v>
@@ -3608,37 +3608,37 @@
         <v>0.143</v>
       </c>
       <c r="M27">
-        <v>0.2684194</v>
+        <v>0.279156176</v>
       </c>
       <c r="N27">
-        <v>-0.1254194</v>
+        <v>-0.136156176</v>
       </c>
       <c r="O27">
-        <v>-0.02508388</v>
+        <v>-0.02723123520000001</v>
       </c>
       <c r="P27">
-        <v>-0.10033552</v>
+        <v>-0.1089249408</v>
       </c>
       <c r="Q27">
-        <v>-0.04333552000000001</v>
+        <v>-0.05192494080000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1097321993555123</v>
+        <v>0.1105961479954517</v>
       </c>
       <c r="T27">
-        <v>1.212770197364835</v>
+        <v>1.229158983815711</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1065496756195715</v>
+        <v>0.1024516111726649</v>
       </c>
       <c r="W27">
-        <v>0.1794048251355901</v>
+        <v>0.1802277164765289</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5327483780978572</v>
+        <v>0.5122580558633243</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3654,22 +3654,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1287003558005317</v>
+        <v>0.1398951260613737</v>
       </c>
       <c r="C28">
-        <v>1.826097333942616</v>
+        <v>1.404368446491972</v>
       </c>
       <c r="D28">
-        <v>3.095317333942616</v>
+        <v>2.727058446491972</v>
       </c>
       <c r="E28">
-        <v>1.24322</v>
+        <v>1.29669</v>
       </c>
       <c r="F28">
-        <v>1.39022</v>
+        <v>1.44369</v>
       </c>
       <c r="G28">
         <v>0.121</v>
@@ -3690,45 +3690,45 @@
         <v>0.143</v>
       </c>
       <c r="M28">
-        <v>0.279156176</v>
+        <v>0.3404221020000001</v>
       </c>
       <c r="N28">
-        <v>-0.136156176</v>
+        <v>-0.197422102</v>
       </c>
       <c r="O28">
-        <v>-0.02723123520000001</v>
+        <v>-0.03948442040000001</v>
       </c>
       <c r="P28">
-        <v>-0.1089249408</v>
+        <v>-0.1579376816</v>
       </c>
       <c r="Q28">
-        <v>-0.05192494080000001</v>
+        <v>-0.1009376816000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1105961479954517</v>
+        <v>0.1117505750376387</v>
       </c>
       <c r="T28">
-        <v>1.229158983815711</v>
+        <v>1.251058038218815</v>
       </c>
       <c r="U28">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1024516111726649</v>
+        <v>0.08401334646597064</v>
       </c>
       <c r="W28">
-        <v>0.1802277164765289</v>
+        <v>0.2159896529033241</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.5122580558633243</v>
+        <v>0.4200667323298533</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3736,22 +3736,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1398951260613737</v>
+        <v>0.1417951260613738</v>
       </c>
       <c r="C29">
-        <v>1.404368446491972</v>
+        <v>1.296922674378062</v>
       </c>
       <c r="D29">
-        <v>2.727058446491972</v>
+        <v>2.673082674378062</v>
       </c>
       <c r="E29">
-        <v>1.29669</v>
+        <v>1.35016</v>
       </c>
       <c r="F29">
-        <v>1.44369</v>
+        <v>1.49716</v>
       </c>
       <c r="G29">
         <v>0.121</v>
@@ -3772,37 +3772,37 @@
         <v>0.143</v>
       </c>
       <c r="M29">
-        <v>0.3404221020000001</v>
+        <v>0.3530303280000001</v>
       </c>
       <c r="N29">
-        <v>-0.197422102</v>
+        <v>-0.210030328</v>
       </c>
       <c r="O29">
-        <v>-0.03948442040000001</v>
+        <v>-0.04200606560000001</v>
       </c>
       <c r="P29">
-        <v>-0.1579376816</v>
+        <v>-0.1680242624</v>
       </c>
       <c r="Q29">
-        <v>-0.1009376816000001</v>
+        <v>-0.1110242624</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1117505750376387</v>
+        <v>0.1126665552464948</v>
       </c>
       <c r="T29">
-        <v>1.251058038218815</v>
+        <v>1.268433844305187</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.08401334646597064</v>
+        <v>0.0810128698064717</v>
       </c>
       <c r="W29">
-        <v>0.2159896529033241</v>
+        <v>0.216697165299634</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4200667323298533</v>
+        <v>0.4050643490323584</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3818,22 +3818,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1417951260613738</v>
+        <v>0.1436951260613737</v>
       </c>
       <c r="C30">
-        <v>1.296922674378062</v>
+        <v>1.191572082507387</v>
       </c>
       <c r="D30">
-        <v>2.673082674378062</v>
+        <v>2.621202082507388</v>
       </c>
       <c r="E30">
-        <v>1.35016</v>
+        <v>1.40363</v>
       </c>
       <c r="F30">
-        <v>1.49716</v>
+        <v>1.55063</v>
       </c>
       <c r="G30">
         <v>0.121</v>
@@ -3854,37 +3854,37 @@
         <v>0.143</v>
       </c>
       <c r="M30">
-        <v>0.3530303280000001</v>
+        <v>0.3656385540000001</v>
       </c>
       <c r="N30">
-        <v>-0.210030328</v>
+        <v>-0.2226385540000001</v>
       </c>
       <c r="O30">
-        <v>-0.04200606560000001</v>
+        <v>-0.04452771080000002</v>
       </c>
       <c r="P30">
-        <v>-0.1680242624</v>
+        <v>-0.1781108432000001</v>
       </c>
       <c r="Q30">
-        <v>-0.1110242624</v>
+        <v>-0.1211108432000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1126665552464948</v>
+        <v>0.1136083377147553</v>
       </c>
       <c r="T30">
-        <v>1.268433844305187</v>
+        <v>1.286299109717937</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.0810128698064717</v>
+        <v>0.07821932257176577</v>
       </c>
       <c r="W30">
-        <v>0.216697165299634</v>
+        <v>0.2173558837375776</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4050643490323584</v>
+        <v>0.3910966128588288</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3900,22 +3900,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1436951260613737</v>
+        <v>0.1455951260613738</v>
       </c>
       <c r="C31">
-        <v>1.191572082507388</v>
+        <v>1.088197000432526</v>
       </c>
       <c r="D31">
-        <v>2.621202082507388</v>
+        <v>2.571297000432526</v>
       </c>
       <c r="E31">
-        <v>1.40363</v>
+        <v>1.4571</v>
       </c>
       <c r="F31">
-        <v>1.55063</v>
+        <v>1.6041</v>
       </c>
       <c r="G31">
         <v>0.121</v>
@@ -3936,37 +3936,37 @@
         <v>0.143</v>
       </c>
       <c r="M31">
-        <v>0.365638554</v>
+        <v>0.3782467800000001</v>
       </c>
       <c r="N31">
-        <v>-0.222638554</v>
+        <v>-0.23524678</v>
       </c>
       <c r="O31">
-        <v>-0.0445277108</v>
+        <v>-0.04704935600000001</v>
       </c>
       <c r="P31">
-        <v>-0.1781108432</v>
+        <v>-0.188197424</v>
       </c>
       <c r="Q31">
-        <v>-0.1211108432</v>
+        <v>-0.131197424</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1136083377147553</v>
+        <v>0.1145770282535375</v>
       </c>
       <c r="T31">
-        <v>1.286299109717937</v>
+        <v>1.304674811285336</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.07821932257176578</v>
+        <v>0.07561201181937359</v>
       </c>
       <c r="W31">
-        <v>0.2173558837375776</v>
+        <v>0.2179706876129917</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3910966128588289</v>
+        <v>0.3780600590968679</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3982,22 +3982,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1455951260613738</v>
+        <v>0.1474951260613737</v>
       </c>
       <c r="C32">
-        <v>1.088197000432526</v>
+        <v>0.986686701058952</v>
       </c>
       <c r="D32">
-        <v>2.571297000432526</v>
+        <v>2.523256701058952</v>
       </c>
       <c r="E32">
-        <v>1.4571</v>
+        <v>1.51057</v>
       </c>
       <c r="F32">
-        <v>1.6041</v>
+        <v>1.65757</v>
       </c>
       <c r="G32">
         <v>0.121</v>
@@ -4018,37 +4018,37 @@
         <v>0.143</v>
       </c>
       <c r="M32">
-        <v>0.3782467800000001</v>
+        <v>0.3908550060000001</v>
       </c>
       <c r="N32">
-        <v>-0.23524678</v>
+        <v>-0.247855006</v>
       </c>
       <c r="O32">
-        <v>-0.04704935600000001</v>
+        <v>-0.04957100120000001</v>
       </c>
       <c r="P32">
-        <v>-0.188197424</v>
+        <v>-0.1982840048</v>
       </c>
       <c r="Q32">
-        <v>-0.131197424</v>
+        <v>-0.1412840048</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1145770282535375</v>
+        <v>0.1155737967789511</v>
       </c>
       <c r="T32">
-        <v>1.304674811285336</v>
+        <v>1.323583141883674</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.07561201181937359</v>
+        <v>0.07317291466390992</v>
       </c>
       <c r="W32">
-        <v>0.2179706876129917</v>
+        <v>0.21854582672225</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3780600590968679</v>
+        <v>0.3658645733195496</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4064,22 +4064,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1474951260613737</v>
+        <v>0.1493951260613737</v>
       </c>
       <c r="C33">
-        <v>0.986686701058952</v>
+        <v>0.886938580511353</v>
       </c>
       <c r="D33">
-        <v>2.523256701058952</v>
+        <v>2.476978580511353</v>
       </c>
       <c r="E33">
-        <v>1.51057</v>
+        <v>1.56404</v>
       </c>
       <c r="F33">
-        <v>1.65757</v>
+        <v>1.71104</v>
       </c>
       <c r="G33">
         <v>0.121</v>
@@ -4100,37 +4100,37 @@
         <v>0.143</v>
       </c>
       <c r="M33">
-        <v>0.3908550060000001</v>
+        <v>0.4034632320000001</v>
       </c>
       <c r="N33">
-        <v>-0.247855006</v>
+        <v>-0.260463232</v>
       </c>
       <c r="O33">
-        <v>-0.04957100120000001</v>
+        <v>-0.05209264640000001</v>
       </c>
       <c r="P33">
-        <v>-0.1982840048</v>
+        <v>-0.2083705856</v>
       </c>
       <c r="Q33">
-        <v>-0.1412840048</v>
+        <v>-0.1513705856000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1155737967789511</v>
+        <v>0.1165998820257003</v>
       </c>
       <c r="T33">
-        <v>1.323583141883674</v>
+        <v>1.343047599852551</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.07317291466390992</v>
+        <v>0.07088626108066275</v>
       </c>
       <c r="W33">
-        <v>0.21854582672225</v>
+        <v>0.2190850196371797</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3658645733195496</v>
+        <v>0.3544313054033137</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4146,22 +4146,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1493951260613737</v>
+        <v>0.1512951260613737</v>
       </c>
       <c r="C34">
-        <v>0.886938580511353</v>
+        <v>0.7888574266251183</v>
       </c>
       <c r="D34">
-        <v>2.476978580511353</v>
+        <v>2.432367426625119</v>
       </c>
       <c r="E34">
-        <v>1.56404</v>
+        <v>1.61751</v>
       </c>
       <c r="F34">
-        <v>1.71104</v>
+        <v>1.76451</v>
       </c>
       <c r="G34">
         <v>0.121</v>
@@ -4182,37 +4182,37 @@
         <v>0.143</v>
       </c>
       <c r="M34">
-        <v>0.4034632320000001</v>
+        <v>0.4160714580000001</v>
       </c>
       <c r="N34">
-        <v>-0.260463232</v>
+        <v>-0.273071458</v>
       </c>
       <c r="O34">
-        <v>-0.05209264640000001</v>
+        <v>-0.05461429160000001</v>
       </c>
       <c r="P34">
-        <v>-0.2083705856</v>
+        <v>-0.2184571664</v>
       </c>
       <c r="Q34">
-        <v>-0.1513705856000001</v>
+        <v>-0.1614571664</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1165998820257003</v>
+        <v>0.1176565966828003</v>
       </c>
       <c r="T34">
-        <v>1.343047599852551</v>
+        <v>1.363093086417515</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.07088626108066275</v>
+        <v>0.06873819256306689</v>
       </c>
       <c r="W34">
-        <v>0.2190850196371797</v>
+        <v>0.2195915341936288</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3544313054033137</v>
+        <v>0.3436909628153345</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4228,22 +4228,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1512951260613737</v>
+        <v>0.1531951260613738</v>
       </c>
       <c r="C35">
-        <v>0.7888574266251183</v>
+        <v>0.692354765087511</v>
       </c>
       <c r="D35">
-        <v>2.432367426625119</v>
+        <v>2.389334765087511</v>
       </c>
       <c r="E35">
-        <v>1.61751</v>
+        <v>1.67098</v>
       </c>
       <c r="F35">
-        <v>1.76451</v>
+        <v>1.81798</v>
       </c>
       <c r="G35">
         <v>0.121</v>
@@ -4264,37 +4264,37 @@
         <v>0.143</v>
       </c>
       <c r="M35">
-        <v>0.4160714580000001</v>
+        <v>0.4286796840000001</v>
       </c>
       <c r="N35">
-        <v>-0.273071458</v>
+        <v>-0.2856796840000001</v>
       </c>
       <c r="O35">
-        <v>-0.05461429160000001</v>
+        <v>-0.05713593680000002</v>
       </c>
       <c r="P35">
-        <v>-0.2184571664</v>
+        <v>-0.2285437472000001</v>
       </c>
       <c r="Q35">
-        <v>-0.1614571664</v>
+        <v>-0.1715437472000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1176565966828003</v>
+        <v>0.1187453329961761</v>
       </c>
       <c r="T35">
-        <v>1.363093086417515</v>
+        <v>1.383746011969295</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.06873819256306689</v>
+        <v>0.06671648101709433</v>
       </c>
       <c r="W35">
-        <v>0.2195915341936288</v>
+        <v>0.2200682537761691</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3436909628153345</v>
+        <v>0.3335824050854717</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4310,22 +4310,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1531951260613738</v>
+        <v>0.1550951260613737</v>
       </c>
       <c r="C36">
-        <v>0.692354765087511</v>
+        <v>0.5973482737794087</v>
       </c>
       <c r="D36">
-        <v>2.389334765087511</v>
+        <v>2.347798273779409</v>
       </c>
       <c r="E36">
-        <v>1.67098</v>
+        <v>1.72445</v>
       </c>
       <c r="F36">
-        <v>1.81798</v>
+        <v>1.87145</v>
       </c>
       <c r="G36">
         <v>0.121</v>
@@ -4346,37 +4346,37 @@
         <v>0.143</v>
       </c>
       <c r="M36">
-        <v>0.4286796840000001</v>
+        <v>0.4412879100000001</v>
       </c>
       <c r="N36">
-        <v>-0.2856796840000001</v>
+        <v>-0.29828791</v>
       </c>
       <c r="O36">
-        <v>-0.05713593680000002</v>
+        <v>-0.05965758200000001</v>
       </c>
       <c r="P36">
-        <v>-0.2285437472000001</v>
+        <v>-0.238630328</v>
       </c>
       <c r="Q36">
-        <v>-0.1715437472000001</v>
+        <v>-0.181630328</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1187453329961761</v>
+        <v>0.119867568888425</v>
       </c>
       <c r="T36">
-        <v>1.383746011969295</v>
+        <v>1.405034412153438</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.06671648101709433</v>
+        <v>0.06481029584517736</v>
       </c>
       <c r="W36">
-        <v>0.2200682537761691</v>
+        <v>0.2205177322397072</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3335824050854717</v>
+        <v>0.3240514792258867</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4392,22 +4392,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1550951260613737</v>
+        <v>0.1569951260613738</v>
       </c>
       <c r="C37">
-        <v>0.5973482737794087</v>
+        <v>0.5037612571601835</v>
       </c>
       <c r="D37">
-        <v>2.347798273779409</v>
+        <v>2.307681257160184</v>
       </c>
       <c r="E37">
-        <v>1.72445</v>
+        <v>1.77792</v>
       </c>
       <c r="F37">
-        <v>1.87145</v>
+        <v>1.92492</v>
       </c>
       <c r="G37">
         <v>0.121</v>
@@ -4428,37 +4428,37 @@
         <v>0.143</v>
       </c>
       <c r="M37">
-        <v>0.4412879100000001</v>
+        <v>0.4538961360000001</v>
       </c>
       <c r="N37">
-        <v>-0.29828791</v>
+        <v>-0.3108961360000001</v>
       </c>
       <c r="O37">
-        <v>-0.05965758200000001</v>
+        <v>-0.06217922720000002</v>
       </c>
       <c r="P37">
-        <v>-0.238630328</v>
+        <v>-0.2487169088000001</v>
       </c>
       <c r="Q37">
-        <v>-0.181630328</v>
+        <v>-0.1917169088000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.119867568888425</v>
+        <v>0.1210248746523066</v>
       </c>
       <c r="T37">
-        <v>1.405034412153438</v>
+        <v>1.426988074843336</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.06481029584517736</v>
+        <v>0.06301000984947798</v>
       </c>
       <c r="W37">
-        <v>0.2205177322397072</v>
+        <v>0.2209422396774931</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3240514792258867</v>
+        <v>0.3150500492473899</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4474,22 +4474,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1569951260613738</v>
+        <v>0.1588951260613738</v>
       </c>
       <c r="C38">
-        <v>0.5037612571601837</v>
+        <v>0.4115221736346486</v>
       </c>
       <c r="D38">
-        <v>2.307681257160184</v>
+        <v>2.268912173634649</v>
       </c>
       <c r="E38">
-        <v>1.77792</v>
+        <v>1.83139</v>
       </c>
       <c r="F38">
-        <v>1.92492</v>
+        <v>1.97839</v>
       </c>
       <c r="G38">
         <v>0.121</v>
@@ -4510,37 +4510,37 @@
         <v>0.143</v>
       </c>
       <c r="M38">
-        <v>0.4538961360000001</v>
+        <v>0.4665043620000001</v>
       </c>
       <c r="N38">
-        <v>-0.310896136</v>
+        <v>-0.323504362</v>
       </c>
       <c r="O38">
-        <v>-0.06217922720000001</v>
+        <v>-0.06470087240000001</v>
       </c>
       <c r="P38">
-        <v>-0.2487169088</v>
+        <v>-0.2588034896</v>
       </c>
       <c r="Q38">
-        <v>-0.1917169088</v>
+        <v>-0.2018034896000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1210248746523066</v>
+        <v>0.1222189202817083</v>
       </c>
       <c r="T38">
-        <v>1.426988074843336</v>
+        <v>1.449638679205929</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.06301000984947799</v>
+        <v>0.0613070366103029</v>
       </c>
       <c r="W38">
-        <v>0.2209422396774931</v>
+        <v>0.2213438007672906</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3150500492473899</v>
+        <v>0.3065351830515145</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4556,22 +4556,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1588951260613738</v>
+        <v>0.1607951260613737</v>
       </c>
       <c r="C39">
-        <v>0.4115221736346486</v>
+        <v>0.3205642097742936</v>
       </c>
       <c r="D39">
-        <v>2.268912173634649</v>
+        <v>2.231424209774294</v>
       </c>
       <c r="E39">
-        <v>1.83139</v>
+        <v>1.88486</v>
       </c>
       <c r="F39">
-        <v>1.97839</v>
+        <v>2.03186</v>
       </c>
       <c r="G39">
         <v>0.121</v>
@@ -4592,37 +4592,37 @@
         <v>0.143</v>
       </c>
       <c r="M39">
-        <v>0.4665043620000001</v>
+        <v>0.479112588</v>
       </c>
       <c r="N39">
-        <v>-0.323504362</v>
+        <v>-0.336112588</v>
       </c>
       <c r="O39">
-        <v>-0.06470087240000001</v>
+        <v>-0.0672225176</v>
       </c>
       <c r="P39">
-        <v>-0.2588034896</v>
+        <v>-0.2688900704</v>
       </c>
       <c r="Q39">
-        <v>-0.2018034896000001</v>
+        <v>-0.2118900704</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1222189202817083</v>
+        <v>0.1234514835120585</v>
       </c>
       <c r="T39">
-        <v>1.449638679205929</v>
+        <v>1.473019948225379</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0613070366103029</v>
+        <v>0.05969369354161073</v>
       </c>
       <c r="W39">
-        <v>0.2213438007672906</v>
+        <v>0.2217242270628882</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3065351830515145</v>
+        <v>0.2984684677080537</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4638,22 +4638,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1607951260613737</v>
+        <v>0.1626951260613738</v>
       </c>
       <c r="C40">
-        <v>0.3205642097742936</v>
+        <v>0.2308248960618875</v>
       </c>
       <c r="D40">
-        <v>2.231424209774294</v>
+        <v>2.195154896061888</v>
       </c>
       <c r="E40">
-        <v>1.88486</v>
+        <v>1.93833</v>
       </c>
       <c r="F40">
-        <v>2.03186</v>
+        <v>2.08533</v>
       </c>
       <c r="G40">
         <v>0.121</v>
@@ -4674,37 +4674,37 @@
         <v>0.143</v>
       </c>
       <c r="M40">
-        <v>0.479112588</v>
+        <v>0.4917208140000001</v>
       </c>
       <c r="N40">
-        <v>-0.336112588</v>
+        <v>-0.3487208140000001</v>
       </c>
       <c r="O40">
-        <v>-0.0672225176</v>
+        <v>-0.06974416280000002</v>
       </c>
       <c r="P40">
-        <v>-0.2688900704</v>
+        <v>-0.2789766512000001</v>
       </c>
       <c r="Q40">
-        <v>-0.2118900704</v>
+        <v>-0.2219766512000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1234514835120585</v>
+        <v>0.1247244586516004</v>
       </c>
       <c r="T40">
-        <v>1.473019948225379</v>
+        <v>1.497167816229074</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.05969369354161073</v>
+        <v>0.05816308601490276</v>
       </c>
       <c r="W40">
-        <v>0.2217242270628882</v>
+        <v>0.2220851443176859</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2984684677080537</v>
+        <v>0.2908154300745137</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4720,22 +4720,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1626951260613738</v>
+        <v>0.1645951260613737</v>
       </c>
       <c r="C41">
-        <v>0.2308248960618875</v>
+        <v>0.1422457595105882</v>
       </c>
       <c r="D41">
-        <v>2.195154896061888</v>
+        <v>2.160045759510588</v>
       </c>
       <c r="E41">
-        <v>1.93833</v>
+        <v>1.9918</v>
       </c>
       <c r="F41">
-        <v>2.08533</v>
+        <v>2.1388</v>
       </c>
       <c r="G41">
         <v>0.121</v>
@@ -4756,37 +4756,37 @@
         <v>0.143</v>
       </c>
       <c r="M41">
-        <v>0.4917208140000001</v>
+        <v>0.5043290400000001</v>
       </c>
       <c r="N41">
-        <v>-0.3487208140000001</v>
+        <v>-0.3613290400000001</v>
       </c>
       <c r="O41">
-        <v>-0.06974416280000002</v>
+        <v>-0.07226580800000003</v>
       </c>
       <c r="P41">
-        <v>-0.2789766512000001</v>
+        <v>-0.2890632320000001</v>
       </c>
       <c r="Q41">
-        <v>-0.2219766512000001</v>
+        <v>-0.2320632320000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1247244586516004</v>
+        <v>0.1260398662957937</v>
       </c>
       <c r="T41">
-        <v>1.497167816229074</v>
+        <v>1.522120613166225</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05816308601490276</v>
+        <v>0.05670900886453019</v>
       </c>
       <c r="W41">
-        <v>0.2220851443176859</v>
+        <v>0.2224280157097438</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2908154300745137</v>
+        <v>0.2835450443226509</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4802,22 +4802,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1645951260613737</v>
+        <v>0.1664951260613737</v>
       </c>
       <c r="C42">
-        <v>0.1422457595105882</v>
+        <v>0.05477200909416169</v>
       </c>
       <c r="D42">
-        <v>2.160045759510588</v>
+        <v>2.126042009094162</v>
       </c>
       <c r="E42">
-        <v>1.9918</v>
+        <v>2.04527</v>
       </c>
       <c r="F42">
-        <v>2.1388</v>
+        <v>2.19227</v>
       </c>
       <c r="G42">
         <v>0.121</v>
@@ -4838,37 +4838,37 @@
         <v>0.143</v>
       </c>
       <c r="M42">
-        <v>0.5043290400000001</v>
+        <v>0.516937266</v>
       </c>
       <c r="N42">
-        <v>-0.3613290400000001</v>
+        <v>-0.373937266</v>
       </c>
       <c r="O42">
-        <v>-0.07226580800000003</v>
+        <v>-0.07478745320000001</v>
       </c>
       <c r="P42">
-        <v>-0.2890632320000001</v>
+        <v>-0.2991498128</v>
       </c>
       <c r="Q42">
-        <v>-0.2320632320000001</v>
+        <v>-0.2421498128</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1260398662957937</v>
+        <v>0.1273998640296207</v>
       </c>
       <c r="T42">
-        <v>1.522120613166225</v>
+        <v>1.547919267626669</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05670900886453019</v>
+        <v>0.05532586230685874</v>
       </c>
       <c r="W42">
-        <v>0.2224280157097438</v>
+        <v>0.2227541616680427</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2835450443226509</v>
+        <v>0.2766293115342936</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4884,22 +4884,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1664951260613737</v>
+        <v>0.1683951260613738</v>
       </c>
       <c r="C43">
-        <v>0.05477200909416169</v>
+        <v>-0.03164774957125838</v>
       </c>
       <c r="D43">
-        <v>2.126042009094162</v>
+        <v>2.093092250428742</v>
       </c>
       <c r="E43">
-        <v>2.04527</v>
+        <v>2.098740000000001</v>
       </c>
       <c r="F43">
-        <v>2.19227</v>
+        <v>2.245740000000001</v>
       </c>
       <c r="G43">
         <v>0.121</v>
@@ -4920,37 +4920,37 @@
         <v>0.143</v>
       </c>
       <c r="M43">
-        <v>0.516937266</v>
+        <v>0.5295454920000001</v>
       </c>
       <c r="N43">
-        <v>-0.373937266</v>
+        <v>-0.3865454920000001</v>
       </c>
       <c r="O43">
-        <v>-0.07478745320000001</v>
+        <v>-0.07730909840000003</v>
       </c>
       <c r="P43">
-        <v>-0.2991498128</v>
+        <v>-0.3092363936000001</v>
       </c>
       <c r="Q43">
-        <v>-0.2421498128</v>
+        <v>-0.2522363936000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1273998640296207</v>
+        <v>0.128806758237028</v>
       </c>
       <c r="T43">
-        <v>1.547919267626669</v>
+        <v>1.574607530861612</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.05532586230685874</v>
+        <v>0.05400857987098112</v>
       </c>
       <c r="W43">
-        <v>0.2227541616680427</v>
+        <v>0.2230647768664227</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2766293115342936</v>
+        <v>0.2700428993549057</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4966,22 +4966,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1683951260613737</v>
+        <v>0.1702951260613738</v>
       </c>
       <c r="C44">
-        <v>-0.03164774957125749</v>
+        <v>-0.1170617734188584</v>
       </c>
       <c r="D44">
-        <v>2.093092250428743</v>
+        <v>2.061148226581142</v>
       </c>
       <c r="E44">
-        <v>2.09874</v>
+        <v>2.15221</v>
       </c>
       <c r="F44">
-        <v>2.24574</v>
+        <v>2.29921</v>
       </c>
       <c r="G44">
         <v>0.121</v>
@@ -5002,37 +5002,37 @@
         <v>0.143</v>
       </c>
       <c r="M44">
-        <v>0.529545492</v>
+        <v>0.542153718</v>
       </c>
       <c r="N44">
-        <v>-0.386545492</v>
+        <v>-0.399153718</v>
       </c>
       <c r="O44">
-        <v>-0.0773090984</v>
+        <v>-0.0798307436</v>
       </c>
       <c r="P44">
-        <v>-0.3092363936</v>
+        <v>-0.3193229744</v>
       </c>
       <c r="Q44">
-        <v>-0.2522363936</v>
+        <v>-0.2623229744</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.128806758237028</v>
+        <v>0.1302630171534671</v>
       </c>
       <c r="T44">
-        <v>1.574607530861612</v>
+        <v>1.6022322243855</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05400857987098114</v>
+        <v>0.05275256638560948</v>
       </c>
       <c r="W44">
-        <v>0.2230647768664226</v>
+        <v>0.2233609448462733</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2700428993549057</v>
+        <v>0.2637628319280474</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5048,22 +5048,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1702951260613738</v>
+        <v>0.1721951260613737</v>
       </c>
       <c r="C45">
-        <v>-0.1170617734188584</v>
+        <v>-0.2015154177454805</v>
       </c>
       <c r="D45">
-        <v>2.061148226581142</v>
+        <v>2.03016458225452</v>
       </c>
       <c r="E45">
-        <v>2.15221</v>
+        <v>2.205680000000001</v>
       </c>
       <c r="F45">
-        <v>2.29921</v>
+        <v>2.35268</v>
       </c>
       <c r="G45">
         <v>0.121</v>
@@ -5084,37 +5084,37 @@
         <v>0.143</v>
       </c>
       <c r="M45">
-        <v>0.542153718</v>
+        <v>0.5547619440000001</v>
       </c>
       <c r="N45">
-        <v>-0.399153718</v>
+        <v>-0.4117619440000001</v>
       </c>
       <c r="O45">
-        <v>-0.0798307436</v>
+        <v>-0.08235238880000002</v>
       </c>
       <c r="P45">
-        <v>-0.3193229744</v>
+        <v>-0.3294095552000001</v>
       </c>
       <c r="Q45">
-        <v>-0.2623229744</v>
+        <v>-0.2724095552000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1302630171534671</v>
+        <v>0.1317712853169218</v>
       </c>
       <c r="T45">
-        <v>1.6022322243855</v>
+        <v>1.63084351410667</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05275256638560948</v>
+        <v>0.05155364442230018</v>
       </c>
       <c r="W45">
-        <v>0.2233609448462733</v>
+        <v>0.2236436506452216</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2637628319280474</v>
+        <v>0.2577682221115009</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5130,22 +5130,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1721951260613737</v>
+        <v>0.1740951260613738</v>
       </c>
       <c r="C46">
-        <v>-0.2015154177454805</v>
+        <v>-0.2850513510720387</v>
       </c>
       <c r="D46">
-        <v>2.03016458225452</v>
+        <v>2.000098648927962</v>
       </c>
       <c r="E46">
-        <v>2.205680000000001</v>
+        <v>2.25915</v>
       </c>
       <c r="F46">
-        <v>2.35268</v>
+        <v>2.40615</v>
       </c>
       <c r="G46">
         <v>0.121</v>
@@ -5166,37 +5166,37 @@
         <v>0.143</v>
       </c>
       <c r="M46">
-        <v>0.5547619440000001</v>
+        <v>0.5673701700000001</v>
       </c>
       <c r="N46">
-        <v>-0.4117619440000001</v>
+        <v>-0.4243701700000001</v>
       </c>
       <c r="O46">
-        <v>-0.08235238880000002</v>
+        <v>-0.08487403400000003</v>
       </c>
       <c r="P46">
-        <v>-0.3294095552000001</v>
+        <v>-0.3394961360000001</v>
       </c>
       <c r="Q46">
-        <v>-0.2724095552000001</v>
+        <v>-0.2824961360000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1317712853169218</v>
+        <v>0.1333343995954114</v>
       </c>
       <c r="T46">
-        <v>1.63084351410667</v>
+        <v>1.660495214363154</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05155364442230018</v>
+        <v>0.05040800787958238</v>
       </c>
       <c r="W46">
-        <v>0.2236436506452216</v>
+        <v>0.2239137917419945</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2577682221115009</v>
+        <v>0.252040039397912</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5212,22 +5212,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1740951260613738</v>
+        <v>0.1759951260613737</v>
       </c>
       <c r="C47">
-        <v>-0.2850513510720387</v>
+        <v>-0.3677097511905787</v>
       </c>
       <c r="D47">
-        <v>2.000098648927962</v>
+        <v>1.970910248809422</v>
       </c>
       <c r="E47">
-        <v>2.25915</v>
+        <v>2.31262</v>
       </c>
       <c r="F47">
-        <v>2.40615</v>
+        <v>2.45962</v>
       </c>
       <c r="G47">
         <v>0.121</v>
@@ -5248,37 +5248,37 @@
         <v>0.143</v>
       </c>
       <c r="M47">
-        <v>0.5673701700000001</v>
+        <v>0.579978396</v>
       </c>
       <c r="N47">
-        <v>-0.4243701700000001</v>
+        <v>-0.436978396</v>
       </c>
       <c r="O47">
-        <v>-0.08487403400000003</v>
+        <v>-0.08739567920000001</v>
       </c>
       <c r="P47">
-        <v>-0.3394961360000001</v>
+        <v>-0.3495827168</v>
       </c>
       <c r="Q47">
-        <v>-0.2824961360000001</v>
+        <v>-0.2925827168</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1333343995954114</v>
+        <v>0.1349554069953264</v>
       </c>
       <c r="T47">
-        <v>1.660495214363154</v>
+        <v>1.69124512574025</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05040800787958238</v>
+        <v>0.04931218162133061</v>
       </c>
       <c r="W47">
-        <v>0.2239137917419945</v>
+        <v>0.2241721875736902</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.252040039397912</v>
+        <v>0.246560908106653</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5294,22 +5294,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1759951260613737</v>
+        <v>0.1778951260613738</v>
       </c>
       <c r="C48">
-        <v>-0.3677097511905787</v>
+        <v>-0.4495284842921925</v>
       </c>
       <c r="D48">
-        <v>1.970910248809422</v>
+        <v>1.942561515707808</v>
       </c>
       <c r="E48">
-        <v>2.31262</v>
+        <v>2.366090000000001</v>
       </c>
       <c r="F48">
-        <v>2.45962</v>
+        <v>2.51309</v>
       </c>
       <c r="G48">
         <v>0.121</v>
@@ -5330,37 +5330,37 @@
         <v>0.143</v>
       </c>
       <c r="M48">
-        <v>0.579978396</v>
+        <v>0.5925866220000001</v>
       </c>
       <c r="N48">
-        <v>-0.436978396</v>
+        <v>-0.4495866220000001</v>
       </c>
       <c r="O48">
-        <v>-0.08739567920000001</v>
+        <v>-0.08991732440000003</v>
       </c>
       <c r="P48">
-        <v>-0.3495827168</v>
+        <v>-0.3596692976000001</v>
       </c>
       <c r="Q48">
-        <v>-0.2925827168</v>
+        <v>-0.3026692976000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1349554069953264</v>
+        <v>0.1366375844858042</v>
       </c>
       <c r="T48">
-        <v>1.69124512574025</v>
+        <v>1.723155411131575</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04931218162133061</v>
+        <v>0.04826298626768527</v>
       </c>
       <c r="W48">
-        <v>0.2241721875736902</v>
+        <v>0.2244195878380798</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.246560908106653</v>
+        <v>0.2413149313384263</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5376,22 +5376,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1778951260613738</v>
+        <v>0.1797951260613738</v>
       </c>
       <c r="C49">
-        <v>-0.4495284842921925</v>
+        <v>-0.5305432688551348</v>
       </c>
       <c r="D49">
-        <v>1.942561515707808</v>
+        <v>1.915016731144866</v>
       </c>
       <c r="E49">
-        <v>2.366090000000001</v>
+        <v>2.419560000000001</v>
       </c>
       <c r="F49">
-        <v>2.51309</v>
+        <v>2.56656</v>
       </c>
       <c r="G49">
         <v>0.121</v>
@@ -5412,37 +5412,37 @@
         <v>0.143</v>
       </c>
       <c r="M49">
-        <v>0.5925866220000001</v>
+        <v>0.6051948480000001</v>
       </c>
       <c r="N49">
-        <v>-0.4495866220000001</v>
+        <v>-0.4621948480000001</v>
       </c>
       <c r="O49">
-        <v>-0.08991732440000003</v>
+        <v>-0.09243896960000003</v>
       </c>
       <c r="P49">
-        <v>-0.3596692976000001</v>
+        <v>-0.3697558784000001</v>
       </c>
       <c r="Q49">
-        <v>-0.3026692976000001</v>
+        <v>-0.3127558784000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1366375844858042</v>
+        <v>0.1383844611105312</v>
       </c>
       <c r="T49">
-        <v>1.723155411131575</v>
+        <v>1.756293015191798</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04826298626768527</v>
+        <v>0.04725750738710849</v>
       </c>
       <c r="W49">
-        <v>0.2244195878380798</v>
+        <v>0.2246566797581198</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2413149313384263</v>
+        <v>0.2362875369355424</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5458,22 +5458,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1797951260613737</v>
+        <v>0.1816951260613738</v>
       </c>
       <c r="C50">
-        <v>-0.5305432688551344</v>
+        <v>-0.6107878257846604</v>
       </c>
       <c r="D50">
-        <v>1.915016731144866</v>
+        <v>1.88824217421534</v>
       </c>
       <c r="E50">
-        <v>2.41956</v>
+        <v>2.473030000000001</v>
       </c>
       <c r="F50">
-        <v>2.56656</v>
+        <v>2.62003</v>
       </c>
       <c r="G50">
         <v>0.121</v>
@@ -5494,37 +5494,37 @@
         <v>0.143</v>
       </c>
       <c r="M50">
-        <v>0.605194848</v>
+        <v>0.6178030740000001</v>
       </c>
       <c r="N50">
-        <v>-0.462194848</v>
+        <v>-0.4748030740000001</v>
       </c>
       <c r="O50">
-        <v>-0.0924389696</v>
+        <v>-0.09496061480000002</v>
       </c>
       <c r="P50">
-        <v>-0.3697558784</v>
+        <v>-0.3798424592000001</v>
       </c>
       <c r="Q50">
-        <v>-0.3127558784</v>
+        <v>-0.3228424592000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1383844611105312</v>
+        <v>0.1401998427009338</v>
       </c>
       <c r="T50">
-        <v>1.756293015191798</v>
+        <v>1.790730133136735</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0472575073871085</v>
+        <v>0.04629306846084097</v>
       </c>
       <c r="W50">
-        <v>0.2246566797581198</v>
+        <v>0.2248840944569337</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2362875369355425</v>
+        <v>0.2314653423042048</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5540,22 +5540,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1816951260613738</v>
+        <v>0.1835951260613737</v>
       </c>
       <c r="C51">
-        <v>-0.6107878257846604</v>
+        <v>-0.6902940161315607</v>
       </c>
       <c r="D51">
-        <v>1.88824217421534</v>
+        <v>1.862205983868439</v>
       </c>
       <c r="E51">
-        <v>2.473030000000001</v>
+        <v>2.5265</v>
       </c>
       <c r="F51">
-        <v>2.62003</v>
+        <v>2.6735</v>
       </c>
       <c r="G51">
         <v>0.121</v>
@@ -5576,37 +5576,37 @@
         <v>0.143</v>
       </c>
       <c r="M51">
-        <v>0.6178030740000001</v>
+        <v>0.6304113000000001</v>
       </c>
       <c r="N51">
-        <v>-0.4748030740000001</v>
+        <v>-0.4874113000000001</v>
       </c>
       <c r="O51">
-        <v>-0.09496061480000002</v>
+        <v>-0.09748226000000003</v>
       </c>
       <c r="P51">
-        <v>-0.3798424592000001</v>
+        <v>-0.3899290400000001</v>
       </c>
       <c r="Q51">
-        <v>-0.3228424592000001</v>
+        <v>-0.3329290400000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1401998427009338</v>
+        <v>0.1420878395549525</v>
       </c>
       <c r="T51">
-        <v>1.790730133136735</v>
+        <v>1.82654473579947</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04629306846084097</v>
+        <v>0.04536720709162415</v>
       </c>
       <c r="W51">
-        <v>0.2248840944569337</v>
+        <v>0.225102412567795</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2314653423042048</v>
+        <v>0.2268360354581207</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5622,22 +5622,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1835951260613737</v>
+        <v>0.1854951260613737</v>
       </c>
       <c r="C52">
-        <v>-0.6902940161315607</v>
+        <v>-0.7690919675720107</v>
       </c>
       <c r="D52">
-        <v>1.862205983868439</v>
+        <v>1.836878032427989</v>
       </c>
       <c r="E52">
-        <v>2.5265</v>
+        <v>2.57997</v>
       </c>
       <c r="F52">
-        <v>2.6735</v>
+        <v>2.72697</v>
       </c>
       <c r="G52">
         <v>0.121</v>
@@ -5658,37 +5658,37 @@
         <v>0.143</v>
       </c>
       <c r="M52">
-        <v>0.6304113000000001</v>
+        <v>0.643019526</v>
       </c>
       <c r="N52">
-        <v>-0.4874113000000001</v>
+        <v>-0.500019526</v>
       </c>
       <c r="O52">
-        <v>-0.09748226000000003</v>
+        <v>-0.1000039052</v>
       </c>
       <c r="P52">
-        <v>-0.3899290400000001</v>
+        <v>-0.4000156208</v>
       </c>
       <c r="Q52">
-        <v>-0.3329290400000001</v>
+        <v>-0.3430156208</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1420878395549525</v>
+        <v>0.1440528975050535</v>
       </c>
       <c r="T52">
-        <v>1.82654473579947</v>
+        <v>1.863821158979051</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04536720709162415</v>
+        <v>0.04447765401139623</v>
       </c>
       <c r="W52">
-        <v>0.225102412567795</v>
+        <v>0.2253121691841128</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2268360354581207</v>
+        <v>0.2223882700569811</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5704,22 +5704,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1854951260613737</v>
+        <v>0.1873951260613738</v>
       </c>
       <c r="C53">
-        <v>-0.7690919675720107</v>
+        <v>-0.8472101907043557</v>
       </c>
       <c r="D53">
-        <v>1.836878032427989</v>
+        <v>1.812229809295645</v>
       </c>
       <c r="E53">
-        <v>2.57997</v>
+        <v>2.633440000000001</v>
       </c>
       <c r="F53">
-        <v>2.72697</v>
+        <v>2.78044</v>
       </c>
       <c r="G53">
         <v>0.121</v>
@@ -5740,37 +5740,37 @@
         <v>0.143</v>
       </c>
       <c r="M53">
-        <v>0.643019526</v>
+        <v>0.6556277520000001</v>
       </c>
       <c r="N53">
-        <v>-0.500019526</v>
+        <v>-0.5126277520000001</v>
       </c>
       <c r="O53">
-        <v>-0.1000039052</v>
+        <v>-0.1025255504</v>
       </c>
       <c r="P53">
-        <v>-0.4000156208</v>
+        <v>-0.4101022016000001</v>
       </c>
       <c r="Q53">
-        <v>-0.3430156208</v>
+        <v>-0.3531022016000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1440528975050535</v>
+        <v>0.1460998328697422</v>
       </c>
       <c r="T53">
-        <v>1.863821158979051</v>
+        <v>1.902650766457781</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04447765401139623</v>
+        <v>0.04362231451117707</v>
       </c>
       <c r="W53">
-        <v>0.2253121691841128</v>
+        <v>0.2255138582382645</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2223882700569811</v>
+        <v>0.2181115725558853</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5786,22 +5786,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1873951260613738</v>
+        <v>0.1892951260613738</v>
       </c>
       <c r="C54">
-        <v>-0.8472101907043557</v>
+        <v>-0.9246756861066807</v>
       </c>
       <c r="D54">
-        <v>1.812229809295645</v>
+        <v>1.78823431389332</v>
       </c>
       <c r="E54">
-        <v>2.633440000000001</v>
+        <v>2.686910000000001</v>
       </c>
       <c r="F54">
-        <v>2.78044</v>
+        <v>2.83391</v>
       </c>
       <c r="G54">
         <v>0.121</v>
@@ -5822,37 +5822,37 @@
         <v>0.143</v>
       </c>
       <c r="M54">
-        <v>0.6556277520000001</v>
+        <v>0.6682359780000001</v>
       </c>
       <c r="N54">
-        <v>-0.5126277520000001</v>
+        <v>-0.5252359780000001</v>
       </c>
       <c r="O54">
-        <v>-0.1025255504</v>
+        <v>-0.1050471956</v>
       </c>
       <c r="P54">
-        <v>-0.4101022016000001</v>
+        <v>-0.4201887824000001</v>
       </c>
       <c r="Q54">
-        <v>-0.3531022016000001</v>
+        <v>-0.3631887824000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1460998328697422</v>
+        <v>0.1482338718669707</v>
       </c>
       <c r="T54">
-        <v>1.902650766457781</v>
+        <v>1.943132697659011</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04362231451117707</v>
+        <v>0.04279925197323033</v>
       </c>
       <c r="W54">
-        <v>0.2255138582382645</v>
+        <v>0.2257079363847123</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2181115725558853</v>
+        <v>0.2139962598661517</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5868,22 +5868,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1892951260613738</v>
+        <v>0.1911951260613738</v>
       </c>
       <c r="C55">
-        <v>-0.9246756861066807</v>
+        <v>-1.001514043000316</v>
       </c>
       <c r="D55">
-        <v>1.78823431389332</v>
+        <v>1.764865956999684</v>
       </c>
       <c r="E55">
-        <v>2.686910000000001</v>
+        <v>2.74038</v>
       </c>
       <c r="F55">
-        <v>2.83391</v>
+        <v>2.88738</v>
       </c>
       <c r="G55">
         <v>0.121</v>
@@ -5904,37 +5904,37 @@
         <v>0.143</v>
       </c>
       <c r="M55">
-        <v>0.6682359780000001</v>
+        <v>0.6808442040000001</v>
       </c>
       <c r="N55">
-        <v>-0.5252359780000001</v>
+        <v>-0.5378442040000001</v>
       </c>
       <c r="O55">
-        <v>-0.1050471956</v>
+        <v>-0.1075688408</v>
       </c>
       <c r="P55">
-        <v>-0.4201887824000001</v>
+        <v>-0.4302753632000001</v>
       </c>
       <c r="Q55">
-        <v>-0.3631887824000001</v>
+        <v>-0.3732753632000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1482338718669707</v>
+        <v>0.1504606951684266</v>
       </c>
       <c r="T55">
-        <v>1.943132697659011</v>
+        <v>1.985374712825511</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04279925197323033</v>
+        <v>0.04200667323298532</v>
       </c>
       <c r="W55">
-        <v>0.2257079363847123</v>
+        <v>0.2258948264516621</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2139962598661517</v>
+        <v>0.2100333661649266</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5950,22 +5950,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1911951260613738</v>
+        <v>0.1930951260613737</v>
       </c>
       <c r="C56">
-        <v>-1.001514043000316</v>
+        <v>-1.077749530277215</v>
       </c>
       <c r="D56">
-        <v>1.764865956999684</v>
+        <v>1.742100469722786</v>
       </c>
       <c r="E56">
-        <v>2.74038</v>
+        <v>2.793850000000001</v>
       </c>
       <c r="F56">
-        <v>2.88738</v>
+        <v>2.940850000000001</v>
       </c>
       <c r="G56">
         <v>0.121</v>
@@ -5986,37 +5986,37 @@
         <v>0.143</v>
       </c>
       <c r="M56">
-        <v>0.6808442040000001</v>
+        <v>0.6934524300000002</v>
       </c>
       <c r="N56">
-        <v>-0.5378442040000001</v>
+        <v>-0.5504524300000002</v>
       </c>
       <c r="O56">
-        <v>-0.1075688408</v>
+        <v>-0.110090486</v>
       </c>
       <c r="P56">
-        <v>-0.4302753632000001</v>
+        <v>-0.4403619440000002</v>
       </c>
       <c r="Q56">
-        <v>-0.3732753632000001</v>
+        <v>-0.3833619440000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1504606951684266</v>
+        <v>0.1527864883943916</v>
       </c>
       <c r="T56">
-        <v>1.985374712825511</v>
+        <v>2.0294941508883</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04200667323298532</v>
+        <v>0.04124291553784013</v>
       </c>
       <c r="W56">
-        <v>0.2258948264516621</v>
+        <v>0.2260749205161773</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2100333661649266</v>
+        <v>0.2062145776892006</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6032,22 +6032,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1930951260613737</v>
+        <v>0.1949951260613738</v>
       </c>
       <c r="C57">
-        <v>-1.077749530277215</v>
+        <v>-1.153405180571928</v>
       </c>
       <c r="D57">
-        <v>1.742100469722786</v>
+        <v>1.719914819428073</v>
       </c>
       <c r="E57">
-        <v>2.793850000000001</v>
+        <v>2.847320000000001</v>
       </c>
       <c r="F57">
-        <v>2.940850000000001</v>
+        <v>2.994320000000001</v>
       </c>
       <c r="G57">
         <v>0.121</v>
@@ -6068,37 +6068,37 @@
         <v>0.143</v>
       </c>
       <c r="M57">
-        <v>0.6934524300000002</v>
+        <v>0.7060606560000001</v>
       </c>
       <c r="N57">
-        <v>-0.5504524300000002</v>
+        <v>-0.5630606560000001</v>
       </c>
       <c r="O57">
-        <v>-0.110090486</v>
+        <v>-0.1126121312</v>
       </c>
       <c r="P57">
-        <v>-0.4403619440000002</v>
+        <v>-0.4504485248000001</v>
       </c>
       <c r="Q57">
-        <v>-0.3833619440000002</v>
+        <v>-0.3934485248000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1527864883943916</v>
+        <v>0.1552179994942642</v>
       </c>
       <c r="T57">
-        <v>2.0294941508883</v>
+        <v>2.075619017953943</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04124291553784013</v>
+        <v>0.04050643490323585</v>
       </c>
       <c r="W57">
-        <v>0.2260749205161773</v>
+        <v>0.226248582649817</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2062145776892006</v>
+        <v>0.2025321745161792</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6114,22 +6114,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1949951260613738</v>
+        <v>0.1968951260613738</v>
       </c>
       <c r="C58">
-        <v>-1.153405180571928</v>
+        <v>-1.228502867990422</v>
       </c>
       <c r="D58">
-        <v>1.719914819428073</v>
+        <v>1.698287132009578</v>
       </c>
       <c r="E58">
-        <v>2.847320000000001</v>
+        <v>2.900790000000001</v>
       </c>
       <c r="F58">
-        <v>2.994320000000001</v>
+        <v>3.04779</v>
       </c>
       <c r="G58">
         <v>0.121</v>
@@ -6150,37 +6150,37 @@
         <v>0.143</v>
       </c>
       <c r="M58">
-        <v>0.7060606560000001</v>
+        <v>0.7186688820000001</v>
       </c>
       <c r="N58">
-        <v>-0.5630606560000001</v>
+        <v>-0.5756688820000001</v>
       </c>
       <c r="O58">
-        <v>-0.1126121312</v>
+        <v>-0.1151337764</v>
       </c>
       <c r="P58">
-        <v>-0.4504485248000001</v>
+        <v>-0.4605351056000001</v>
       </c>
       <c r="Q58">
-        <v>-0.3934485248000001</v>
+        <v>-0.4035351056000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1552179994942642</v>
+        <v>0.1577626041336657</v>
       </c>
       <c r="T58">
-        <v>2.075619017953943</v>
+        <v>2.123889227673803</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04050643490323585</v>
+        <v>0.03979579569440715</v>
       </c>
       <c r="W58">
-        <v>0.226248582649817</v>
+        <v>0.2264161513752588</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2025321745161792</v>
+        <v>0.1989789784720357</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6196,22 +6196,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1968951260613738</v>
+        <v>0.1987951260613738</v>
       </c>
       <c r="C59">
-        <v>-1.228502867990422</v>
+        <v>-1.303063380047151</v>
       </c>
       <c r="D59">
-        <v>1.698287132009578</v>
+        <v>1.677196619952849</v>
       </c>
       <c r="E59">
-        <v>2.900790000000001</v>
+        <v>2.954260000000001</v>
       </c>
       <c r="F59">
-        <v>3.04779</v>
+        <v>3.101260000000001</v>
       </c>
       <c r="G59">
         <v>0.121</v>
@@ -6232,37 +6232,37 @@
         <v>0.143</v>
       </c>
       <c r="M59">
-        <v>0.7186688820000001</v>
+        <v>0.7312771080000002</v>
       </c>
       <c r="N59">
-        <v>-0.5756688820000001</v>
+        <v>-0.5882771080000002</v>
       </c>
       <c r="O59">
-        <v>-0.1151337764</v>
+        <v>-0.1176554216</v>
       </c>
       <c r="P59">
-        <v>-0.4605351056000001</v>
+        <v>-0.4706216864000002</v>
       </c>
       <c r="Q59">
-        <v>-0.4035351056000001</v>
+        <v>-0.4136216864000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1577626041336657</v>
+        <v>0.1604283804225625</v>
       </c>
       <c r="T59">
-        <v>2.123889227673803</v>
+        <v>2.174458018808893</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03979579569440715</v>
+        <v>0.03910966128588288</v>
       </c>
       <c r="W59">
-        <v>0.2264161513752588</v>
+        <v>0.2265779418687888</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1989789784720357</v>
+        <v>0.1955483064294145</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6278,22 +6278,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1987951260613737</v>
+        <v>0.2006951260613737</v>
       </c>
       <c r="C60">
-        <v>-1.30306338004715</v>
+        <v>-1.377106484307693</v>
       </c>
       <c r="D60">
-        <v>1.677196619952849</v>
+        <v>1.656623515692307</v>
       </c>
       <c r="E60">
-        <v>2.95426</v>
+        <v>3.00773</v>
       </c>
       <c r="F60">
-        <v>3.10126</v>
+        <v>3.15473</v>
       </c>
       <c r="G60">
         <v>0.121</v>
@@ -6314,37 +6314,37 @@
         <v>0.143</v>
       </c>
       <c r="M60">
-        <v>0.731277108</v>
+        <v>0.7438853340000001</v>
       </c>
       <c r="N60">
-        <v>-0.588277108</v>
+        <v>-0.6008853340000001</v>
       </c>
       <c r="O60">
-        <v>-0.1176554216</v>
+        <v>-0.1201770668</v>
       </c>
       <c r="P60">
-        <v>-0.4706216864</v>
+        <v>-0.4807082672000001</v>
       </c>
       <c r="Q60">
-        <v>-0.4136216864</v>
+        <v>-0.4237082672000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1604283804225624</v>
+        <v>0.1632241945792103</v>
       </c>
       <c r="T60">
-        <v>2.174458018808892</v>
+        <v>2.227493580243256</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03910966128588289</v>
+        <v>0.03844678567086793</v>
       </c>
       <c r="W60">
-        <v>0.2265779418687888</v>
+        <v>0.2267342479388094</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1955483064294145</v>
+        <v>0.1922339283543396</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6360,22 +6360,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2006951260613737</v>
+        <v>0.2025951260613738</v>
       </c>
       <c r="C61">
-        <v>-1.377106484307693</v>
+        <v>-1.450650990186041</v>
       </c>
       <c r="D61">
-        <v>1.656623515692307</v>
+        <v>1.636549009813959</v>
       </c>
       <c r="E61">
-        <v>3.00773</v>
+        <v>3.0612</v>
       </c>
       <c r="F61">
-        <v>3.15473</v>
+        <v>3.2082</v>
       </c>
       <c r="G61">
         <v>0.121</v>
@@ -6396,37 +6396,37 @@
         <v>0.143</v>
       </c>
       <c r="M61">
-        <v>0.7438853340000001</v>
+        <v>0.7564935600000001</v>
       </c>
       <c r="N61">
-        <v>-0.6008853340000001</v>
+        <v>-0.6134935600000001</v>
       </c>
       <c r="O61">
-        <v>-0.1201770668</v>
+        <v>-0.122698712</v>
       </c>
       <c r="P61">
-        <v>-0.4807082672000001</v>
+        <v>-0.4907948480000001</v>
       </c>
       <c r="Q61">
-        <v>-0.4237082672000001</v>
+        <v>-0.4337948480000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1632241945792103</v>
+        <v>0.1661597994436906</v>
       </c>
       <c r="T61">
-        <v>2.227493580243256</v>
+        <v>2.283180919749337</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03844678567086793</v>
+        <v>0.03780600590968679</v>
       </c>
       <c r="W61">
-        <v>0.2267342479388094</v>
+        <v>0.2268853438064959</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1922339283543396</v>
+        <v>0.189030029548434</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6442,22 +6442,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2025951260613738</v>
+        <v>0.2044951260613738</v>
       </c>
       <c r="C62">
-        <v>-1.450650990186041</v>
+        <v>-1.523714806302637</v>
       </c>
       <c r="D62">
-        <v>1.636549009813959</v>
+        <v>1.616955193697363</v>
       </c>
       <c r="E62">
-        <v>3.0612</v>
+        <v>3.11467</v>
       </c>
       <c r="F62">
-        <v>3.2082</v>
+        <v>3.26167</v>
       </c>
       <c r="G62">
         <v>0.121</v>
@@ -6478,37 +6478,37 @@
         <v>0.143</v>
       </c>
       <c r="M62">
-        <v>0.7564935600000001</v>
+        <v>0.769101786</v>
       </c>
       <c r="N62">
-        <v>-0.6134935600000001</v>
+        <v>-0.626101786</v>
       </c>
       <c r="O62">
-        <v>-0.122698712</v>
+        <v>-0.1252203572</v>
       </c>
       <c r="P62">
-        <v>-0.4907948480000001</v>
+        <v>-0.5008814288</v>
       </c>
       <c r="Q62">
-        <v>-0.4337948480000001</v>
+        <v>-0.4438814288</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1661597994436906</v>
+        <v>0.169245948147375</v>
       </c>
       <c r="T62">
-        <v>2.283180919749337</v>
+        <v>2.341724020255731</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03780600590968679</v>
+        <v>0.03718623532100341</v>
       </c>
       <c r="W62">
-        <v>0.2268853438064959</v>
+        <v>0.2270314857113074</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.189030029548434</v>
+        <v>0.185931176605017</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6524,22 +6524,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2044951260613738</v>
+        <v>0.2063951260613738</v>
       </c>
       <c r="C63">
-        <v>-1.523714806302637</v>
+        <v>-1.596314993770785</v>
       </c>
       <c r="D63">
-        <v>1.616955193697363</v>
+        <v>1.597825006229215</v>
       </c>
       <c r="E63">
-        <v>3.11467</v>
+        <v>3.168140000000001</v>
       </c>
       <c r="F63">
-        <v>3.26167</v>
+        <v>3.31514</v>
       </c>
       <c r="G63">
         <v>0.121</v>
@@ -6560,37 +6560,37 @@
         <v>0.143</v>
       </c>
       <c r="M63">
-        <v>0.769101786</v>
+        <v>0.7817100120000001</v>
       </c>
       <c r="N63">
-        <v>-0.626101786</v>
+        <v>-0.6387100120000001</v>
       </c>
       <c r="O63">
-        <v>-0.1252203572</v>
+        <v>-0.1277420024</v>
       </c>
       <c r="P63">
-        <v>-0.5008814288</v>
+        <v>-0.5109680096000001</v>
       </c>
       <c r="Q63">
-        <v>-0.4438814288</v>
+        <v>-0.4539680096000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.169245948147375</v>
+        <v>0.1724945257302006</v>
       </c>
       <c r="T63">
-        <v>2.341724020255731</v>
+        <v>2.40334833657825</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03718623532100341</v>
+        <v>0.03658645733195496</v>
       </c>
       <c r="W63">
-        <v>0.2270314857113074</v>
+        <v>0.227172913361125</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.185931176605017</v>
+        <v>0.1829322866597748</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6606,22 +6606,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2063951260613738</v>
+        <v>0.2082951260613738</v>
       </c>
       <c r="C64">
-        <v>-1.596314993770785</v>
+        <v>-1.668467815744712</v>
       </c>
       <c r="D64">
-        <v>1.597825006229215</v>
+        <v>1.579142184255288</v>
       </c>
       <c r="E64">
-        <v>3.168140000000001</v>
+        <v>3.221610000000001</v>
       </c>
       <c r="F64">
-        <v>3.31514</v>
+        <v>3.36861</v>
       </c>
       <c r="G64">
         <v>0.121</v>
@@ -6642,37 +6642,37 @@
         <v>0.143</v>
       </c>
       <c r="M64">
-        <v>0.7817100120000001</v>
+        <v>0.7943182380000001</v>
       </c>
       <c r="N64">
-        <v>-0.6387100120000001</v>
+        <v>-0.6513182380000001</v>
       </c>
       <c r="O64">
-        <v>-0.1277420024</v>
+        <v>-0.1302636476</v>
       </c>
       <c r="P64">
-        <v>-0.5109680096000001</v>
+        <v>-0.5210545904000001</v>
       </c>
       <c r="Q64">
-        <v>-0.4539680096000001</v>
+        <v>-0.4640545904000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1724945257302006</v>
+        <v>0.1759187021012872</v>
       </c>
       <c r="T64">
-        <v>2.40334833657825</v>
+        <v>2.468303697026311</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03658645733195496</v>
+        <v>0.03600571991398743</v>
       </c>
       <c r="W64">
-        <v>0.227172913361125</v>
+        <v>0.2273098512442818</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1829322866597748</v>
+        <v>0.1800285995699371</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6688,22 +6688,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2082951260613738</v>
+        <v>0.2101951260613737</v>
       </c>
       <c r="C65">
-        <v>-1.668467815744712</v>
+        <v>-1.740188783531707</v>
       </c>
       <c r="D65">
-        <v>1.579142184255288</v>
+        <v>1.560891216468294</v>
       </c>
       <c r="E65">
-        <v>3.221610000000001</v>
+        <v>3.27508</v>
       </c>
       <c r="F65">
-        <v>3.36861</v>
+        <v>3.42208</v>
       </c>
       <c r="G65">
         <v>0.121</v>
@@ -6724,37 +6724,37 @@
         <v>0.143</v>
       </c>
       <c r="M65">
-        <v>0.7943182380000001</v>
+        <v>0.8069264640000001</v>
       </c>
       <c r="N65">
-        <v>-0.6513182380000001</v>
+        <v>-0.6639264640000001</v>
       </c>
       <c r="O65">
-        <v>-0.1302636476</v>
+        <v>-0.1327852928</v>
       </c>
       <c r="P65">
-        <v>-0.5210545904000001</v>
+        <v>-0.5311411712</v>
       </c>
       <c r="Q65">
-        <v>-0.4640545904000001</v>
+        <v>-0.4741411712</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1759187021012872</v>
+        <v>0.1795331104929896</v>
       </c>
       <c r="T65">
-        <v>2.468303697026311</v>
+        <v>2.536867688610375</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03600571991398743</v>
+        <v>0.03544313054033137</v>
       </c>
       <c r="W65">
-        <v>0.2273098512442818</v>
+        <v>0.2274425098185899</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1800285995699371</v>
+        <v>0.1772156527016568</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6770,22 +6770,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2101951260613737</v>
+        <v>0.2120951260613738</v>
       </c>
       <c r="C66">
-        <v>-1.740188783531707</v>
+        <v>-1.811492699543144</v>
       </c>
       <c r="D66">
-        <v>1.560891216468294</v>
+        <v>1.543057300456857</v>
       </c>
       <c r="E66">
-        <v>3.27508</v>
+        <v>3.328550000000001</v>
       </c>
       <c r="F66">
-        <v>3.42208</v>
+        <v>3.475550000000001</v>
       </c>
       <c r="G66">
         <v>0.121</v>
@@ -6806,37 +6806,37 @@
         <v>0.143</v>
       </c>
       <c r="M66">
-        <v>0.8069264640000001</v>
+        <v>0.8195346900000001</v>
       </c>
       <c r="N66">
-        <v>-0.6639264640000001</v>
+        <v>-0.6765346900000001</v>
       </c>
       <c r="O66">
-        <v>-0.1327852928</v>
+        <v>-0.135306938</v>
       </c>
       <c r="P66">
-        <v>-0.5311411712</v>
+        <v>-0.5412277520000001</v>
       </c>
       <c r="Q66">
-        <v>-0.4741411712</v>
+        <v>-0.4842277520000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1795331104929896</v>
+        <v>0.183354056507075</v>
       </c>
       <c r="T66">
-        <v>2.536867688610375</v>
+        <v>2.609349622570672</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03544313054033137</v>
+        <v>0.03489785160894165</v>
       </c>
       <c r="W66">
-        <v>0.2274425098185899</v>
+        <v>0.2275710865906116</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1772156527016568</v>
+        <v>0.1744892580447083</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6852,22 +6852,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2120951260613738</v>
+        <v>0.2139951260613738</v>
       </c>
       <c r="C67">
-        <v>-1.811492699543144</v>
+        <v>-1.882393697334353</v>
       </c>
       <c r="D67">
-        <v>1.543057300456857</v>
+        <v>1.525626302665648</v>
       </c>
       <c r="E67">
-        <v>3.328550000000001</v>
+        <v>3.382020000000001</v>
       </c>
       <c r="F67">
-        <v>3.475550000000001</v>
+        <v>3.52902</v>
       </c>
       <c r="G67">
         <v>0.121</v>
@@ -6888,37 +6888,37 @@
         <v>0.143</v>
       </c>
       <c r="M67">
-        <v>0.8195346900000001</v>
+        <v>0.8321429160000001</v>
       </c>
       <c r="N67">
-        <v>-0.6765346900000001</v>
+        <v>-0.6891429160000001</v>
       </c>
       <c r="O67">
-        <v>-0.135306938</v>
+        <v>-0.1378285832</v>
       </c>
       <c r="P67">
-        <v>-0.5412277520000001</v>
+        <v>-0.5513143328000001</v>
       </c>
       <c r="Q67">
-        <v>-0.4842277520000001</v>
+        <v>-0.4943143328000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.183354056507075</v>
+        <v>0.1873997640514007</v>
       </c>
       <c r="T67">
-        <v>2.609349622570672</v>
+        <v>2.686095199705103</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03489785160894165</v>
+        <v>0.03436909628153344</v>
       </c>
       <c r="W67">
-        <v>0.2275710865906116</v>
+        <v>0.2276957670968144</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1744892580447083</v>
+        <v>0.1718454814076672</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6934,22 +6934,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2139951260613738</v>
+        <v>0.2158951260613738</v>
       </c>
       <c r="C68">
-        <v>-1.882393697334353</v>
+        <v>-1.952905278960971</v>
       </c>
       <c r="D68">
-        <v>1.525626302665648</v>
+        <v>1.50858472103903</v>
       </c>
       <c r="E68">
-        <v>3.382020000000001</v>
+        <v>3.435490000000001</v>
       </c>
       <c r="F68">
-        <v>3.52902</v>
+        <v>3.58249</v>
       </c>
       <c r="G68">
         <v>0.121</v>
@@ -6970,37 +6970,37 @@
         <v>0.143</v>
       </c>
       <c r="M68">
-        <v>0.8321429160000001</v>
+        <v>0.8447511420000001</v>
       </c>
       <c r="N68">
-        <v>-0.6891429160000001</v>
+        <v>-0.7017511420000001</v>
       </c>
       <c r="O68">
-        <v>-0.1378285832</v>
+        <v>-0.1403502284</v>
       </c>
       <c r="P68">
-        <v>-0.5513143328000001</v>
+        <v>-0.5614009136000001</v>
       </c>
       <c r="Q68">
-        <v>-0.4943143328000001</v>
+        <v>-0.5044009136000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1873997640514007</v>
+        <v>0.1916906659923523</v>
       </c>
       <c r="T68">
-        <v>2.686095199705103</v>
+        <v>2.767492023938591</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03436909628153344</v>
+        <v>0.0338561246952419</v>
       </c>
       <c r="W68">
-        <v>0.2276957670968144</v>
+        <v>0.227816725796862</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1718454814076672</v>
+        <v>0.1692806234762095</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7016,22 +7016,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2158951260613738</v>
+        <v>0.2177951260613738</v>
       </c>
       <c r="C69">
-        <v>-1.952905278960971</v>
+        <v>-2.023040349859267</v>
       </c>
       <c r="D69">
-        <v>1.50858472103903</v>
+        <v>1.491919650140734</v>
       </c>
       <c r="E69">
-        <v>3.435490000000001</v>
+        <v>3.488960000000001</v>
       </c>
       <c r="F69">
-        <v>3.58249</v>
+        <v>3.635960000000001</v>
       </c>
       <c r="G69">
         <v>0.121</v>
@@ -7052,37 +7052,37 @@
         <v>0.143</v>
       </c>
       <c r="M69">
-        <v>0.8447511420000001</v>
+        <v>0.8573593680000002</v>
       </c>
       <c r="N69">
-        <v>-0.7017511420000001</v>
+        <v>-0.7143593680000002</v>
       </c>
       <c r="O69">
-        <v>-0.1403502284</v>
+        <v>-0.1428718736000001</v>
       </c>
       <c r="P69">
-        <v>-0.5614009136000001</v>
+        <v>-0.5714874944000001</v>
       </c>
       <c r="Q69">
-        <v>-0.5044009136000001</v>
+        <v>-0.5144874944000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1916906659923523</v>
+        <v>0.1962497493046133</v>
       </c>
       <c r="T69">
-        <v>2.767492023938591</v>
+        <v>2.853976149686672</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0338561246952419</v>
+        <v>0.03335824050854717</v>
       </c>
       <c r="W69">
-        <v>0.227816725796862</v>
+        <v>0.2279341268880846</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1692806234762095</v>
+        <v>0.1667912025427358</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7098,22 +7098,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2177951260613738</v>
+        <v>0.2196951260613738</v>
       </c>
       <c r="C70">
-        <v>-2.023040349859267</v>
+        <v>-2.092811251439837</v>
       </c>
       <c r="D70">
-        <v>1.491919650140734</v>
+        <v>1.475618748560163</v>
       </c>
       <c r="E70">
-        <v>3.488960000000001</v>
+        <v>3.542430000000001</v>
       </c>
       <c r="F70">
-        <v>3.635960000000001</v>
+        <v>3.689430000000001</v>
       </c>
       <c r="G70">
         <v>0.121</v>
@@ -7134,37 +7134,37 @@
         <v>0.143</v>
       </c>
       <c r="M70">
-        <v>0.8573593680000002</v>
+        <v>0.8699675940000002</v>
       </c>
       <c r="N70">
-        <v>-0.7143593680000002</v>
+        <v>-0.7269675940000002</v>
       </c>
       <c r="O70">
-        <v>-0.1428718736000001</v>
+        <v>-0.1453935188</v>
       </c>
       <c r="P70">
-        <v>-0.5714874944000001</v>
+        <v>-0.5815740752000002</v>
       </c>
       <c r="Q70">
-        <v>-0.5144874944000001</v>
+        <v>-0.5245740752000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1962497493046133</v>
+        <v>0.2011029670241169</v>
       </c>
       <c r="T70">
-        <v>2.853976149686672</v>
+        <v>2.946039896450758</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03335824050854717</v>
+        <v>0.03287478774755373</v>
       </c>
       <c r="W70">
-        <v>0.2279341268880846</v>
+        <v>0.2280481250491269</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1667912025427358</v>
+        <v>0.1643739387377686</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7180,22 +7180,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2196951260613738</v>
+        <v>0.2215951260613738</v>
       </c>
       <c r="C71">
-        <v>-2.092811251439837</v>
+        <v>-2.162229791567654</v>
       </c>
       <c r="D71">
-        <v>1.475618748560163</v>
+        <v>1.459670208432347</v>
       </c>
       <c r="E71">
-        <v>3.542430000000001</v>
+        <v>3.595900000000001</v>
       </c>
       <c r="F71">
-        <v>3.689430000000001</v>
+        <v>3.742900000000001</v>
       </c>
       <c r="G71">
         <v>0.121</v>
@@ -7216,37 +7216,37 @@
         <v>0.143</v>
       </c>
       <c r="M71">
-        <v>0.8699675940000002</v>
+        <v>0.8825758200000001</v>
       </c>
       <c r="N71">
-        <v>-0.7269675940000002</v>
+        <v>-0.7395758200000001</v>
       </c>
       <c r="O71">
-        <v>-0.1453935188</v>
+        <v>-0.147915164</v>
       </c>
       <c r="P71">
-        <v>-0.5815740752000002</v>
+        <v>-0.5916606560000001</v>
       </c>
       <c r="Q71">
-        <v>-0.5245740752000001</v>
+        <v>-0.534660656</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2011029670241169</v>
+        <v>0.2062797325915875</v>
       </c>
       <c r="T71">
-        <v>2.946039896450758</v>
+        <v>3.044241226332451</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03287478774755373</v>
+        <v>0.03240514792258868</v>
       </c>
       <c r="W71">
-        <v>0.2280481250491269</v>
+        <v>0.2281588661198536</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1643739387377686</v>
+        <v>0.1620257396129434</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7262,22 +7262,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2215951260613738</v>
+        <v>0.2234951260613738</v>
       </c>
       <c r="C72">
-        <v>-2.162229791567654</v>
+        <v>-2.231307273086666</v>
       </c>
       <c r="D72">
-        <v>1.459670208432347</v>
+        <v>1.444062726913335</v>
       </c>
       <c r="E72">
-        <v>3.595900000000001</v>
+        <v>3.649370000000001</v>
       </c>
       <c r="F72">
-        <v>3.742900000000001</v>
+        <v>3.796370000000001</v>
       </c>
       <c r="G72">
         <v>0.121</v>
@@ -7298,37 +7298,37 @@
         <v>0.143</v>
       </c>
       <c r="M72">
-        <v>0.8825758200000001</v>
+        <v>0.8951840460000002</v>
       </c>
       <c r="N72">
-        <v>-0.7395758200000001</v>
+        <v>-0.7521840460000002</v>
       </c>
       <c r="O72">
-        <v>-0.147915164</v>
+        <v>-0.1504368092</v>
       </c>
       <c r="P72">
-        <v>-0.5916606560000001</v>
+        <v>-0.6017472368000002</v>
       </c>
       <c r="Q72">
-        <v>-0.534660656</v>
+        <v>-0.5447472368000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2062797325915875</v>
+        <v>0.211813516474056</v>
       </c>
       <c r="T72">
-        <v>3.044241226332451</v>
+        <v>3.149215061723225</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03240514792258868</v>
+        <v>0.03194873738846771</v>
       </c>
       <c r="W72">
-        <v>0.2281588661198536</v>
+        <v>0.2282664877237993</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1620257396129434</v>
+        <v>0.1597436869423385</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7344,22 +7344,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2234951260613738</v>
+        <v>0.2253951260613737</v>
       </c>
       <c r="C73">
-        <v>-2.231307273086665</v>
+        <v>-2.30005452053378</v>
       </c>
       <c r="D73">
-        <v>1.444062726913335</v>
+        <v>1.42878547946622</v>
       </c>
       <c r="E73">
-        <v>3.64937</v>
+        <v>3.702840000000001</v>
       </c>
       <c r="F73">
-        <v>3.79637</v>
+        <v>3.84984</v>
       </c>
       <c r="G73">
         <v>0.121</v>
@@ -7380,37 +7380,37 @@
         <v>0.143</v>
       </c>
       <c r="M73">
-        <v>0.895184046</v>
+        <v>0.9077922720000001</v>
       </c>
       <c r="N73">
-        <v>-0.752184046</v>
+        <v>-0.7647922720000001</v>
       </c>
       <c r="O73">
-        <v>-0.1504368092</v>
+        <v>-0.1529584544</v>
       </c>
       <c r="P73">
-        <v>-0.6017472368</v>
+        <v>-0.6118338176000001</v>
       </c>
       <c r="Q73">
-        <v>-0.5447472367999999</v>
+        <v>-0.5548338176000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.211813516474056</v>
+        <v>0.2177425706338437</v>
       </c>
       <c r="T73">
-        <v>3.149215061723224</v>
+        <v>3.261687028213339</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03194873738846771</v>
+        <v>0.031505004924739</v>
       </c>
       <c r="W73">
-        <v>0.2282664877237993</v>
+        <v>0.2283711198387466</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1597436869423385</v>
+        <v>0.157525024623695</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7426,22 +7426,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2253951260613737</v>
+        <v>0.2272951260613738</v>
       </c>
       <c r="C74">
-        <v>-2.30005452053378</v>
+        <v>-2.368481905174885</v>
       </c>
       <c r="D74">
-        <v>1.42878547946622</v>
+        <v>1.413828094825115</v>
       </c>
       <c r="E74">
-        <v>3.702840000000001</v>
+        <v>3.75631</v>
       </c>
       <c r="F74">
-        <v>3.84984</v>
+        <v>3.90331</v>
       </c>
       <c r="G74">
         <v>0.121</v>
@@ -7462,37 +7462,37 @@
         <v>0.143</v>
       </c>
       <c r="M74">
-        <v>0.9077922720000001</v>
+        <v>0.9204004980000001</v>
       </c>
       <c r="N74">
-        <v>-0.7647922720000001</v>
+        <v>-0.7774004980000001</v>
       </c>
       <c r="O74">
-        <v>-0.1529584544</v>
+        <v>-0.1554800996</v>
       </c>
       <c r="P74">
-        <v>-0.6118338176000001</v>
+        <v>-0.6219203984000001</v>
       </c>
       <c r="Q74">
-        <v>-0.5548338176000001</v>
+        <v>-0.5649203984000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2177425706338437</v>
+        <v>0.2241108139906527</v>
       </c>
       <c r="T74">
-        <v>3.261687028213339</v>
+        <v>3.382490251480499</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.031505004924739</v>
+        <v>0.03107342951481106</v>
       </c>
       <c r="W74">
-        <v>0.2283711198387466</v>
+        <v>0.2284728853204075</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.157525024623695</v>
+        <v>0.1553671475740553</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7508,22 +7508,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2272951260613738</v>
+        <v>0.2291951260613737</v>
       </c>
       <c r="C75">
-        <v>-2.368481905174885</v>
+        <v>-2.436599368484617</v>
       </c>
       <c r="D75">
-        <v>1.413828094825115</v>
+        <v>1.399180631515383</v>
       </c>
       <c r="E75">
-        <v>3.75631</v>
+        <v>3.80978</v>
       </c>
       <c r="F75">
-        <v>3.90331</v>
+        <v>3.95678</v>
       </c>
       <c r="G75">
         <v>0.121</v>
@@ -7544,37 +7544,37 @@
         <v>0.143</v>
       </c>
       <c r="M75">
-        <v>0.9204004980000001</v>
+        <v>0.9330087240000001</v>
       </c>
       <c r="N75">
-        <v>-0.7774004980000001</v>
+        <v>-0.7900087240000001</v>
       </c>
       <c r="O75">
-        <v>-0.1554800996</v>
+        <v>-0.1580017448</v>
       </c>
       <c r="P75">
-        <v>-0.6219203984000001</v>
+        <v>-0.6320069792</v>
       </c>
       <c r="Q75">
-        <v>-0.5649203984000001</v>
+        <v>-0.5750069792</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2241108139906527</v>
+        <v>0.2309689222210624</v>
       </c>
       <c r="T75">
-        <v>3.382490251480499</v>
+        <v>3.512586030383595</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03107342951481106</v>
+        <v>0.03065351830515145</v>
       </c>
       <c r="W75">
-        <v>0.2284728853204075</v>
+        <v>0.2285719003836453</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1553671475740553</v>
+        <v>0.1532675915257573</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7590,22 +7590,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2291951260613737</v>
+        <v>0.2310951260613738</v>
       </c>
       <c r="C76">
-        <v>-2.436599368484617</v>
+        <v>-2.504416444181571</v>
       </c>
       <c r="D76">
-        <v>1.399180631515383</v>
+        <v>1.384833555818429</v>
       </c>
       <c r="E76">
-        <v>3.80978</v>
+        <v>3.86325</v>
       </c>
       <c r="F76">
-        <v>3.95678</v>
+        <v>4.01025</v>
       </c>
       <c r="G76">
         <v>0.121</v>
@@ -7626,37 +7626,37 @@
         <v>0.143</v>
       </c>
       <c r="M76">
-        <v>0.9330087240000001</v>
+        <v>0.94561695</v>
       </c>
       <c r="N76">
-        <v>-0.7900087240000001</v>
+        <v>-0.80261695</v>
       </c>
       <c r="O76">
-        <v>-0.1580017448</v>
+        <v>-0.16052339</v>
       </c>
       <c r="P76">
-        <v>-0.6320069792</v>
+        <v>-0.64209356</v>
       </c>
       <c r="Q76">
-        <v>-0.5750069792</v>
+        <v>-0.5850935599999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2309689222210624</v>
+        <v>0.238375679109905</v>
       </c>
       <c r="T76">
-        <v>3.512586030383595</v>
+        <v>3.653089471598939</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03065351830515145</v>
+        <v>0.03024480472774944</v>
       </c>
       <c r="W76">
-        <v>0.2285719003836453</v>
+        <v>0.2286682750451967</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1532675915257573</v>
+        <v>0.1512240236387472</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7672,22 +7672,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2310951260613738</v>
+        <v>0.2329951260613737</v>
       </c>
       <c r="C77">
-        <v>-2.504416444181571</v>
+        <v>-2.571942278921587</v>
       </c>
       <c r="D77">
-        <v>1.384833555818429</v>
+        <v>1.370777721078413</v>
       </c>
       <c r="E77">
-        <v>3.86325</v>
+        <v>3.91672</v>
       </c>
       <c r="F77">
-        <v>4.01025</v>
+        <v>4.06372</v>
       </c>
       <c r="G77">
         <v>0.121</v>
@@ -7708,37 +7708,37 @@
         <v>0.143</v>
       </c>
       <c r="M77">
-        <v>0.94561695</v>
+        <v>0.958225176</v>
       </c>
       <c r="N77">
-        <v>-0.80261695</v>
+        <v>-0.815225176</v>
       </c>
       <c r="O77">
-        <v>-0.16052339</v>
+        <v>-0.1630450352</v>
       </c>
       <c r="P77">
-        <v>-0.64209356</v>
+        <v>-0.6521801408</v>
       </c>
       <c r="Q77">
-        <v>-0.5850935599999999</v>
+        <v>-0.5951801407999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.238375679109905</v>
+        <v>0.2463996657394843</v>
       </c>
       <c r="T77">
-        <v>3.653089471598939</v>
+        <v>3.805301532915562</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03024480472774944</v>
+        <v>0.02984684677080536</v>
       </c>
       <c r="W77">
-        <v>0.2286682750451967</v>
+        <v>0.2287621135314441</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1512240236387472</v>
+        <v>0.1492342338540268</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7754,22 +7754,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2329951260613737</v>
+        <v>0.2348951260613738</v>
       </c>
       <c r="C78">
-        <v>-2.571942278921587</v>
+        <v>-2.639185651743496</v>
       </c>
       <c r="D78">
-        <v>1.370777721078413</v>
+        <v>1.357004348256505</v>
       </c>
       <c r="E78">
-        <v>3.91672</v>
+        <v>3.970190000000001</v>
       </c>
       <c r="F78">
-        <v>4.06372</v>
+        <v>4.117190000000001</v>
       </c>
       <c r="G78">
         <v>0.121</v>
@@ -7790,37 +7790,37 @@
         <v>0.143</v>
       </c>
       <c r="M78">
-        <v>0.958225176</v>
+        <v>0.9708334020000002</v>
       </c>
       <c r="N78">
-        <v>-0.815225176</v>
+        <v>-0.8278334020000002</v>
       </c>
       <c r="O78">
-        <v>-0.1630450352</v>
+        <v>-0.1655666804000001</v>
       </c>
       <c r="P78">
-        <v>-0.6521801408</v>
+        <v>-0.6622667216000002</v>
       </c>
       <c r="Q78">
-        <v>-0.5951801407999999</v>
+        <v>-0.6052667216000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2463996657394843</v>
+        <v>0.2551213903368532</v>
       </c>
       <c r="T78">
-        <v>3.805301532915562</v>
+        <v>3.970749425651022</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02984684677080536</v>
+        <v>0.02945922538417152</v>
       </c>
       <c r="W78">
-        <v>0.2287621135314441</v>
+        <v>0.2288535146544124</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1492342338540268</v>
+        <v>0.1472961269208576</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7836,22 +7836,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2348951260613738</v>
+        <v>0.2367951260613738</v>
       </c>
       <c r="C79">
-        <v>-2.639185651743496</v>
+        <v>-2.706154992354203</v>
       </c>
       <c r="D79">
-        <v>1.357004348256505</v>
+        <v>1.343505007645798</v>
       </c>
       <c r="E79">
-        <v>3.970190000000001</v>
+        <v>4.02366</v>
       </c>
       <c r="F79">
-        <v>4.117190000000001</v>
+        <v>4.170660000000001</v>
       </c>
       <c r="G79">
         <v>0.121</v>
@@ -7872,37 +7872,37 @@
         <v>0.143</v>
       </c>
       <c r="M79">
-        <v>0.9708334020000002</v>
+        <v>0.9834416280000002</v>
       </c>
       <c r="N79">
-        <v>-0.8278334020000002</v>
+        <v>-0.8404416280000002</v>
       </c>
       <c r="O79">
-        <v>-0.1655666804000001</v>
+        <v>-0.1680883256000001</v>
       </c>
       <c r="P79">
-        <v>-0.6622667216000002</v>
+        <v>-0.6723533024000001</v>
       </c>
       <c r="Q79">
-        <v>-0.6052667216000002</v>
+        <v>-0.6153533024000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2551213903368532</v>
+        <v>0.2646359989885284</v>
       </c>
       <c r="T79">
-        <v>3.970749425651022</v>
+        <v>4.151238035907887</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02945922538417152</v>
+        <v>0.02908154300745138</v>
       </c>
       <c r="W79">
-        <v>0.2288535146544124</v>
+        <v>0.228942572158843</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1472961269208576</v>
+        <v>0.1454077150372569</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7918,22 +7918,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2367951260613738</v>
+        <v>0.2386951260613738</v>
       </c>
       <c r="C80">
-        <v>-2.706154992354203</v>
+        <v>-2.772858398333133</v>
       </c>
       <c r="D80">
-        <v>1.343505007645798</v>
+        <v>1.330271601666868</v>
       </c>
       <c r="E80">
-        <v>4.02366</v>
+        <v>4.07713</v>
       </c>
       <c r="F80">
-        <v>4.170660000000001</v>
+        <v>4.224130000000001</v>
       </c>
       <c r="G80">
         <v>0.121</v>
@@ -7954,37 +7954,37 @@
         <v>0.143</v>
       </c>
       <c r="M80">
-        <v>0.9834416280000002</v>
+        <v>0.9960498540000002</v>
       </c>
       <c r="N80">
-        <v>-0.8404416280000002</v>
+        <v>-0.8530498540000002</v>
       </c>
       <c r="O80">
-        <v>-0.1680883256000001</v>
+        <v>-0.1706099708000001</v>
       </c>
       <c r="P80">
-        <v>-0.6723533024000001</v>
+        <v>-0.6824398832000002</v>
       </c>
       <c r="Q80">
-        <v>-0.6153533024000001</v>
+        <v>-0.6254398832000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2646359989885284</v>
+        <v>0.275056760845125</v>
       </c>
       <c r="T80">
-        <v>4.151238035907887</v>
+        <v>4.348916037617786</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02908154300745138</v>
+        <v>0.0287134222098887</v>
       </c>
       <c r="W80">
-        <v>0.228942572158843</v>
+        <v>0.2290293750429082</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1454077150372569</v>
+        <v>0.1435671110494435</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8000,22 +8000,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2386951260613738</v>
+        <v>0.2405951260613738</v>
       </c>
       <c r="C81">
-        <v>-2.772858398333133</v>
+        <v>-2.839303651329815</v>
       </c>
       <c r="D81">
-        <v>1.330271601666868</v>
+        <v>1.317296348670186</v>
       </c>
       <c r="E81">
-        <v>4.07713</v>
+        <v>4.1306</v>
       </c>
       <c r="F81">
-        <v>4.224130000000001</v>
+        <v>4.277600000000001</v>
       </c>
       <c r="G81">
         <v>0.121</v>
@@ -8036,37 +8036,37 @@
         <v>0.143</v>
       </c>
       <c r="M81">
-        <v>0.9960498540000002</v>
+        <v>1.00865808</v>
       </c>
       <c r="N81">
-        <v>-0.8530498540000002</v>
+        <v>-0.8656580800000002</v>
       </c>
       <c r="O81">
-        <v>-0.1706099708000001</v>
+        <v>-0.173131616</v>
       </c>
       <c r="P81">
-        <v>-0.6824398832000002</v>
+        <v>-0.6925264640000002</v>
       </c>
       <c r="Q81">
-        <v>-0.6254398832000001</v>
+        <v>-0.6355264640000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.275056760845125</v>
+        <v>0.2865195988873812</v>
       </c>
       <c r="T81">
-        <v>4.348916037617786</v>
+        <v>4.566361839498676</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0287134222098887</v>
+        <v>0.02835450443226509</v>
       </c>
       <c r="W81">
-        <v>0.2290293750429082</v>
+        <v>0.2291140078548719</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1435671110494435</v>
+        <v>0.1417725221613254</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8082,22 +8082,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2405951260613738</v>
+        <v>0.2424951260613737</v>
       </c>
       <c r="C82">
-        <v>-2.839303651329815</v>
+        <v>-2.905498232322698</v>
       </c>
       <c r="D82">
-        <v>1.317296348670186</v>
+        <v>1.304571767677303</v>
       </c>
       <c r="E82">
-        <v>4.1306</v>
+        <v>4.18407</v>
       </c>
       <c r="F82">
-        <v>4.277600000000001</v>
+        <v>4.33107</v>
       </c>
       <c r="G82">
         <v>0.121</v>
@@ -8118,37 +8118,37 @@
         <v>0.143</v>
       </c>
       <c r="M82">
-        <v>1.00865808</v>
+        <v>1.021266306</v>
       </c>
       <c r="N82">
-        <v>-0.8656580800000002</v>
+        <v>-0.8782663060000002</v>
       </c>
       <c r="O82">
-        <v>-0.173131616</v>
+        <v>-0.1756532612</v>
       </c>
       <c r="P82">
-        <v>-0.6925264640000002</v>
+        <v>-0.7026130448000002</v>
       </c>
       <c r="Q82">
-        <v>-0.6355264640000001</v>
+        <v>-0.6456130448000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2865195988873812</v>
+        <v>0.2991890514604013</v>
       </c>
       <c r="T82">
-        <v>4.566361839498676</v>
+        <v>4.806696673156501</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02835450443226509</v>
+        <v>0.02800444882199021</v>
       </c>
       <c r="W82">
-        <v>0.2291140078548719</v>
+        <v>0.2291965509677747</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1417725221613254</v>
+        <v>0.140022244109951</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8164,22 +8164,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2424951260613737</v>
+        <v>0.2443951260613738</v>
       </c>
       <c r="C83">
-        <v>-2.905498232322698</v>
+        <v>-2.971449336002055</v>
       </c>
       <c r="D83">
-        <v>1.304571767677303</v>
+        <v>1.292090663997945</v>
       </c>
       <c r="E83">
-        <v>4.18407</v>
+        <v>4.23754</v>
       </c>
       <c r="F83">
-        <v>4.33107</v>
+        <v>4.38454</v>
       </c>
       <c r="G83">
         <v>0.121</v>
@@ -8200,37 +8200,37 @@
         <v>0.143</v>
       </c>
       <c r="M83">
-        <v>1.021266306</v>
+        <v>1.033874532</v>
       </c>
       <c r="N83">
-        <v>-0.8782663060000002</v>
+        <v>-0.890874532</v>
       </c>
       <c r="O83">
-        <v>-0.1756532612</v>
+        <v>-0.1781749064</v>
       </c>
       <c r="P83">
-        <v>-0.7026130448000002</v>
+        <v>-0.7126996256</v>
       </c>
       <c r="Q83">
-        <v>-0.6456130448000001</v>
+        <v>-0.6556996255999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2991890514604013</v>
+        <v>0.3132662209859792</v>
       </c>
       <c r="T83">
-        <v>4.806696673156501</v>
+        <v>5.073735377220751</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02800444882199021</v>
+        <v>0.02766293115342937</v>
       </c>
       <c r="W83">
-        <v>0.2291965509677747</v>
+        <v>0.2292770808340214</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.140022244109951</v>
+        <v>0.1383146557671469</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8246,22 +8246,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2443951260613738</v>
+        <v>0.2462951260613738</v>
       </c>
       <c r="C84">
-        <v>-2.971449336002055</v>
+        <v>-3.037163884335088</v>
       </c>
       <c r="D84">
-        <v>1.292090663997945</v>
+        <v>1.279846115664913</v>
       </c>
       <c r="E84">
-        <v>4.23754</v>
+        <v>4.291010000000001</v>
       </c>
       <c r="F84">
-        <v>4.38454</v>
+        <v>4.438010000000001</v>
       </c>
       <c r="G84">
         <v>0.121</v>
@@ -8282,37 +8282,37 @@
         <v>0.143</v>
       </c>
       <c r="M84">
-        <v>1.033874532</v>
+        <v>1.046482758</v>
       </c>
       <c r="N84">
-        <v>-0.890874532</v>
+        <v>-0.9034827580000002</v>
       </c>
       <c r="O84">
-        <v>-0.1781749064</v>
+        <v>-0.1806965516000001</v>
       </c>
       <c r="P84">
-        <v>-0.7126996256</v>
+        <v>-0.7227862064000001</v>
       </c>
       <c r="Q84">
-        <v>-0.6556996255999999</v>
+        <v>-0.6657862064000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3132662209859792</v>
+        <v>0.3289995281028015</v>
       </c>
       <c r="T84">
-        <v>5.073735377220751</v>
+        <v>5.372190399410208</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02766293115342937</v>
+        <v>0.0273296428262796</v>
       </c>
       <c r="W84">
-        <v>0.2292770808340214</v>
+        <v>0.2293556702215633</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1383146557671469</v>
+        <v>0.136648214131398</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8328,22 +8328,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2462951260613738</v>
+        <v>0.2481951260613738</v>
       </c>
       <c r="C85">
-        <v>-3.037163884335088</v>
+        <v>-3.102648539366979</v>
       </c>
       <c r="D85">
-        <v>1.279846115664913</v>
+        <v>1.267831460633022</v>
       </c>
       <c r="E85">
-        <v>4.291010000000001</v>
+        <v>4.344480000000001</v>
       </c>
       <c r="F85">
-        <v>4.438010000000001</v>
+        <v>4.491480000000001</v>
       </c>
       <c r="G85">
         <v>0.121</v>
@@ -8364,37 +8364,37 @@
         <v>0.143</v>
       </c>
       <c r="M85">
-        <v>1.046482758</v>
+        <v>1.059090984</v>
       </c>
       <c r="N85">
-        <v>-0.9034827580000002</v>
+        <v>-0.9160909840000002</v>
       </c>
       <c r="O85">
-        <v>-0.1806965516000001</v>
+        <v>-0.1832181968000001</v>
       </c>
       <c r="P85">
-        <v>-0.7227862064000001</v>
+        <v>-0.7328727872000002</v>
       </c>
       <c r="Q85">
-        <v>-0.6657862064000001</v>
+        <v>-0.6758727872000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3289995281028015</v>
+        <v>0.3466994986092267</v>
       </c>
       <c r="T85">
-        <v>5.372190399410208</v>
+        <v>5.707952299373346</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0273296428262796</v>
+        <v>0.02700428993549056</v>
       </c>
       <c r="W85">
-        <v>0.2293556702215633</v>
+        <v>0.2294323884332113</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.136648214131398</v>
+        <v>0.1350214496774528</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8410,22 +8410,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2481951260613738</v>
+        <v>0.2500951260613737</v>
       </c>
       <c r="C86">
-        <v>-3.102648539366978</v>
+        <v>-3.167909715307608</v>
       </c>
       <c r="D86">
-        <v>1.267831460633022</v>
+        <v>1.256040284692393</v>
       </c>
       <c r="E86">
-        <v>4.34448</v>
+        <v>4.39795</v>
       </c>
       <c r="F86">
-        <v>4.49148</v>
+        <v>4.54495</v>
       </c>
       <c r="G86">
         <v>0.121</v>
@@ -8446,37 +8446,37 @@
         <v>0.143</v>
       </c>
       <c r="M86">
-        <v>1.059090984</v>
+        <v>1.07169921</v>
       </c>
       <c r="N86">
-        <v>-0.916090984</v>
+        <v>-0.92869921</v>
       </c>
       <c r="O86">
-        <v>-0.1832181968</v>
+        <v>-0.185739842</v>
       </c>
       <c r="P86">
-        <v>-0.7328727872</v>
+        <v>-0.742959368</v>
       </c>
       <c r="Q86">
-        <v>-0.6758727872</v>
+        <v>-0.6859593679999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3466994986092264</v>
+        <v>0.3667594651831749</v>
       </c>
       <c r="T86">
-        <v>5.707952299373343</v>
+        <v>6.088482452664898</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02700428993549057</v>
+        <v>0.02668659240683774</v>
       </c>
       <c r="W86">
-        <v>0.2294323884332113</v>
+        <v>0.2295073015104677</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1350214496774529</v>
+        <v>0.1334329620341886</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8492,22 +8492,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2500951260613737</v>
+        <v>0.2519951260613738</v>
       </c>
       <c r="C87">
-        <v>-3.167909715307608</v>
+        <v>-3.232953589950043</v>
       </c>
       <c r="D87">
-        <v>1.256040284692393</v>
+        <v>1.244466410049957</v>
       </c>
       <c r="E87">
-        <v>4.39795</v>
+        <v>4.45142</v>
       </c>
       <c r="F87">
-        <v>4.54495</v>
+        <v>4.59842</v>
       </c>
       <c r="G87">
         <v>0.121</v>
@@ -8528,37 +8528,37 @@
         <v>0.143</v>
       </c>
       <c r="M87">
-        <v>1.07169921</v>
+        <v>1.084307436</v>
       </c>
       <c r="N87">
-        <v>-0.92869921</v>
+        <v>-0.941307436</v>
       </c>
       <c r="O87">
-        <v>-0.185739842</v>
+        <v>-0.1882614872</v>
       </c>
       <c r="P87">
-        <v>-0.742959368</v>
+        <v>-0.7530459488</v>
       </c>
       <c r="Q87">
-        <v>-0.6859593679999999</v>
+        <v>-0.6960459487999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3667594651831749</v>
+        <v>0.3896851412676874</v>
       </c>
       <c r="T87">
-        <v>6.088482452664898</v>
+        <v>6.523374056426678</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02668659240683774</v>
+        <v>0.02637628319280474</v>
       </c>
       <c r="W87">
-        <v>0.2295073015104677</v>
+        <v>0.2295804724231366</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1334329620341886</v>
+        <v>0.1318814159640237</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8574,22 +8574,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2519951260613738</v>
+        <v>0.2538951260613738</v>
       </c>
       <c r="C88">
-        <v>-3.232953589950043</v>
+        <v>-3.297786115463484</v>
       </c>
       <c r="D88">
-        <v>1.244466410049957</v>
+        <v>1.233103884536517</v>
       </c>
       <c r="E88">
-        <v>4.45142</v>
+        <v>4.504890000000001</v>
       </c>
       <c r="F88">
-        <v>4.59842</v>
+        <v>4.651890000000001</v>
       </c>
       <c r="G88">
         <v>0.121</v>
@@ -8610,37 +8610,37 @@
         <v>0.143</v>
       </c>
       <c r="M88">
-        <v>1.084307436</v>
+        <v>1.096915662</v>
       </c>
       <c r="N88">
-        <v>-0.941307436</v>
+        <v>-0.9539156620000002</v>
       </c>
       <c r="O88">
-        <v>-0.1882614872</v>
+        <v>-0.1907831324000001</v>
       </c>
       <c r="P88">
-        <v>-0.7530459488</v>
+        <v>-0.7631325296000002</v>
       </c>
       <c r="Q88">
-        <v>-0.6960459487999999</v>
+        <v>-0.7061325296000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3896851412676874</v>
+        <v>0.4161378444421249</v>
       </c>
       <c r="T88">
-        <v>6.523374056426678</v>
+        <v>7.025172060767192</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02637628319280474</v>
+        <v>0.02607310752392192</v>
       </c>
       <c r="W88">
-        <v>0.2295804724231366</v>
+        <v>0.2296519612458592</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1318814159640237</v>
+        <v>0.1303655376196096</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8656,22 +8656,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2538951260613738</v>
+        <v>0.2557951260613738</v>
       </c>
       <c r="C89">
-        <v>-3.297786115463484</v>
+        <v>-3.36241302860029</v>
       </c>
       <c r="D89">
-        <v>1.233103884536517</v>
+        <v>1.221946971399711</v>
       </c>
       <c r="E89">
-        <v>4.504890000000001</v>
+        <v>4.55836</v>
       </c>
       <c r="F89">
-        <v>4.651890000000001</v>
+        <v>4.705360000000001</v>
       </c>
       <c r="G89">
         <v>0.121</v>
@@ -8692,37 +8692,37 @@
         <v>0.143</v>
       </c>
       <c r="M89">
-        <v>1.096915662</v>
+        <v>1.109523888</v>
       </c>
       <c r="N89">
-        <v>-0.9539156620000002</v>
+        <v>-0.9665238880000002</v>
       </c>
       <c r="O89">
-        <v>-0.1907831324000001</v>
+        <v>-0.1933047776000001</v>
       </c>
       <c r="P89">
-        <v>-0.7631325296000002</v>
+        <v>-0.7732191104000001</v>
       </c>
       <c r="Q89">
-        <v>-0.7061325296000002</v>
+        <v>-0.7162191104000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4161378444421249</v>
+        <v>0.4469993314789686</v>
       </c>
       <c r="T89">
-        <v>7.025172060767192</v>
+        <v>7.610603065831125</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02607310752392192</v>
+        <v>0.02577682221115009</v>
       </c>
       <c r="W89">
-        <v>0.2296519612458592</v>
+        <v>0.2297218253226108</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1303655376196096</v>
+        <v>0.1288841110557504</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8738,22 +8738,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2557951260613738</v>
+        <v>0.2576951260613737</v>
       </c>
       <c r="C90">
-        <v>-3.36241302860029</v>
+        <v>-3.426839860353876</v>
       </c>
       <c r="D90">
-        <v>1.221946971399711</v>
+        <v>1.210990139646125</v>
       </c>
       <c r="E90">
-        <v>4.55836</v>
+        <v>4.61183</v>
       </c>
       <c r="F90">
-        <v>4.705360000000001</v>
+        <v>4.758830000000001</v>
       </c>
       <c r="G90">
         <v>0.121</v>
@@ -8774,37 +8774,37 @@
         <v>0.143</v>
       </c>
       <c r="M90">
-        <v>1.109523888</v>
+        <v>1.122132114</v>
       </c>
       <c r="N90">
-        <v>-0.9665238880000002</v>
+        <v>-0.9791321140000002</v>
       </c>
       <c r="O90">
-        <v>-0.1933047776000001</v>
+        <v>-0.1958264228000001</v>
       </c>
       <c r="P90">
-        <v>-0.7732191104000001</v>
+        <v>-0.7833056912000002</v>
       </c>
       <c r="Q90">
-        <v>-0.7162191104000001</v>
+        <v>-0.7263056912000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4469993314789686</v>
+        <v>0.4834719979770568</v>
       </c>
       <c r="T90">
-        <v>7.610603065831125</v>
+        <v>8.302476071815773</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02577682221115009</v>
+        <v>0.02548719499529447</v>
       </c>
       <c r="W90">
-        <v>0.2297218253226108</v>
+        <v>0.2297901194201096</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1288841110557504</v>
+        <v>0.1274359749764723</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8820,22 +8820,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2576951260613737</v>
+        <v>0.2595951260613737</v>
       </c>
       <c r="C91">
-        <v>-3.426839860353876</v>
+        <v>-3.491071945101623</v>
       </c>
       <c r="D91">
-        <v>1.210990139646125</v>
+        <v>1.200228054898378</v>
       </c>
       <c r="E91">
-        <v>4.61183</v>
+        <v>4.6653</v>
       </c>
       <c r="F91">
-        <v>4.758830000000001</v>
+        <v>4.8123</v>
       </c>
       <c r="G91">
         <v>0.121</v>
@@ -8856,37 +8856,37 @@
         <v>0.143</v>
       </c>
       <c r="M91">
-        <v>1.122132114</v>
+        <v>1.13474034</v>
       </c>
       <c r="N91">
-        <v>-0.9791321140000002</v>
+        <v>-0.9917403400000002</v>
       </c>
       <c r="O91">
-        <v>-0.1958264228000001</v>
+        <v>-0.198348068</v>
       </c>
       <c r="P91">
-        <v>-0.7833056912000002</v>
+        <v>-0.7933922720000002</v>
       </c>
       <c r="Q91">
-        <v>-0.7263056912000001</v>
+        <v>-0.7363922720000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4834719979770568</v>
+        <v>0.5272391977747625</v>
       </c>
       <c r="T91">
-        <v>8.302476071815773</v>
+        <v>9.132723678997351</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02548719499529447</v>
+        <v>0.02520400393979119</v>
       </c>
       <c r="W91">
-        <v>0.2297901194201096</v>
+        <v>0.2298568958709973</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1274359749764723</v>
+        <v>0.1260200196989559</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8902,22 +8902,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2595951260613737</v>
+        <v>0.2614951260613738</v>
       </c>
       <c r="C92">
-        <v>-3.491071945101623</v>
+        <v>-3.555114429264561</v>
       </c>
       <c r="D92">
-        <v>1.200228054898378</v>
+        <v>1.189655570735439</v>
       </c>
       <c r="E92">
-        <v>4.6653</v>
+        <v>4.71877</v>
       </c>
       <c r="F92">
-        <v>4.8123</v>
+        <v>4.86577</v>
       </c>
       <c r="G92">
         <v>0.121</v>
@@ -8938,37 +8938,37 @@
         <v>0.143</v>
       </c>
       <c r="M92">
-        <v>1.13474034</v>
+        <v>1.147348566</v>
       </c>
       <c r="N92">
-        <v>-0.9917403400000002</v>
+        <v>-1.004348566</v>
       </c>
       <c r="O92">
-        <v>-0.198348068</v>
+        <v>-0.2008697132</v>
       </c>
       <c r="P92">
-        <v>-0.7933922720000002</v>
+        <v>-0.8034788528000002</v>
       </c>
       <c r="Q92">
-        <v>-0.7363922720000001</v>
+        <v>-0.7464788528000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5272391977747625</v>
+        <v>0.5807324419719583</v>
       </c>
       <c r="T92">
-        <v>9.132723678997351</v>
+        <v>10.1474707544415</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02520400393979119</v>
+        <v>0.02492703686352975</v>
       </c>
       <c r="W92">
-        <v>0.2298568958709973</v>
+        <v>0.2299222047075797</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1260200196989559</v>
+        <v>0.1246351843176488</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8984,22 +8984,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2614951260613738</v>
+        <v>0.2633951260613738</v>
       </c>
       <c r="C93">
-        <v>-3.555114429264561</v>
+        <v>-3.618972279513375</v>
       </c>
       <c r="D93">
-        <v>1.189655570735439</v>
+        <v>1.179267720486625</v>
       </c>
       <c r="E93">
-        <v>4.71877</v>
+        <v>4.77224</v>
       </c>
       <c r="F93">
-        <v>4.86577</v>
+        <v>4.91924</v>
       </c>
       <c r="G93">
         <v>0.121</v>
@@ -9020,37 +9020,37 @@
         <v>0.143</v>
       </c>
       <c r="M93">
-        <v>1.147348566</v>
+        <v>1.159956792</v>
       </c>
       <c r="N93">
-        <v>-1.004348566</v>
+        <v>-1.016956792</v>
       </c>
       <c r="O93">
-        <v>-0.2008697132</v>
+        <v>-0.2033913584</v>
       </c>
       <c r="P93">
-        <v>-0.8034788528000002</v>
+        <v>-0.8135654336</v>
       </c>
       <c r="Q93">
-        <v>-0.7464788528000001</v>
+        <v>-0.7565654335999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5807324419719583</v>
+        <v>0.6475989972184533</v>
       </c>
       <c r="T93">
-        <v>10.1474707544415</v>
+        <v>11.41590459874669</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02492703686352975</v>
+        <v>0.0246560908106653</v>
       </c>
       <c r="W93">
-        <v>0.2299222047075797</v>
+        <v>0.2299860937868451</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1246351843176488</v>
+        <v>0.1232804540533265</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9066,22 +9066,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2633951260613738</v>
+        <v>0.2652951260613737</v>
       </c>
       <c r="C94">
-        <v>-3.618972279513375</v>
+        <v>-3.682650290548199</v>
       </c>
       <c r="D94">
-        <v>1.179267720486625</v>
+        <v>1.169059709451802</v>
       </c>
       <c r="E94">
-        <v>4.77224</v>
+        <v>4.825710000000001</v>
       </c>
       <c r="F94">
-        <v>4.91924</v>
+        <v>4.972710000000001</v>
       </c>
       <c r="G94">
         <v>0.121</v>
@@ -9102,37 +9102,37 @@
         <v>0.143</v>
       </c>
       <c r="M94">
-        <v>1.159956792</v>
+        <v>1.172565018</v>
       </c>
       <c r="N94">
-        <v>-1.016956792</v>
+        <v>-1.029565018</v>
       </c>
       <c r="O94">
-        <v>-0.2033913584</v>
+        <v>-0.2059130036000001</v>
       </c>
       <c r="P94">
-        <v>-0.8135654336</v>
+        <v>-0.8236520144000001</v>
       </c>
       <c r="Q94">
-        <v>-0.7565654335999999</v>
+        <v>-0.7666520144000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6475989972184533</v>
+        <v>0.7335702825353753</v>
       </c>
       <c r="T94">
-        <v>11.41590459874669</v>
+        <v>13.04674811285336</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0246560908106653</v>
+        <v>0.02439097155463664</v>
       </c>
       <c r="W94">
-        <v>0.2299860937868451</v>
+        <v>0.2300486089074167</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1232804540533265</v>
+        <v>0.1219548577731832</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9148,22 +9148,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2652951260613737</v>
+        <v>0.2671951260613737</v>
       </c>
       <c r="C95">
-        <v>-3.682650290548199</v>
+        <v>-3.746153092477826</v>
       </c>
       <c r="D95">
-        <v>1.169059709451802</v>
+        <v>1.159026907522175</v>
       </c>
       <c r="E95">
-        <v>4.825710000000001</v>
+        <v>4.879180000000001</v>
       </c>
       <c r="F95">
-        <v>4.972710000000001</v>
+        <v>5.026180000000001</v>
       </c>
       <c r="G95">
         <v>0.121</v>
@@ -9184,37 +9184,37 @@
         <v>0.143</v>
       </c>
       <c r="M95">
-        <v>1.172565018</v>
+        <v>1.185173244</v>
       </c>
       <c r="N95">
-        <v>-1.029565018</v>
+        <v>-1.042173244</v>
       </c>
       <c r="O95">
-        <v>-0.2059130036000001</v>
+        <v>-0.2084346488000001</v>
       </c>
       <c r="P95">
-        <v>-0.8236520144000001</v>
+        <v>-0.8337385952000002</v>
       </c>
       <c r="Q95">
-        <v>-0.7666520144000001</v>
+        <v>-0.7767385952000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7335702825353753</v>
+        <v>0.8481986629579379</v>
       </c>
       <c r="T95">
-        <v>13.04674811285336</v>
+        <v>15.22120613166226</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02439097155463664</v>
+        <v>0.02413149313384264</v>
       </c>
       <c r="W95">
-        <v>0.2300486089074167</v>
+        <v>0.2301097939190399</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1219548577731832</v>
+        <v>0.1206574656692132</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9230,22 +9230,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2671951260613737</v>
+        <v>0.2690951260613738</v>
       </c>
       <c r="C96">
-        <v>-3.746153092477826</v>
+        <v>-3.809485157822176</v>
       </c>
       <c r="D96">
-        <v>1.159026907522175</v>
+        <v>1.149164842177825</v>
       </c>
       <c r="E96">
-        <v>4.879180000000001</v>
+        <v>4.932650000000001</v>
       </c>
       <c r="F96">
-        <v>5.026180000000001</v>
+        <v>5.079650000000001</v>
       </c>
       <c r="G96">
         <v>0.121</v>
@@ -9266,37 +9266,37 @@
         <v>0.143</v>
       </c>
       <c r="M96">
-        <v>1.185173244</v>
+        <v>1.19778147</v>
       </c>
       <c r="N96">
-        <v>-1.042173244</v>
+        <v>-1.05478147</v>
       </c>
       <c r="O96">
-        <v>-0.2084346488000001</v>
+        <v>-0.210956294</v>
       </c>
       <c r="P96">
-        <v>-0.8337385952000002</v>
+        <v>-0.8438251760000002</v>
       </c>
       <c r="Q96">
-        <v>-0.7767385952000001</v>
+        <v>-0.7868251760000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8481986629579379</v>
+        <v>1.008678395549526</v>
       </c>
       <c r="T96">
-        <v>15.22120613166226</v>
+        <v>18.26544735799472</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02413149313384264</v>
+        <v>0.02387747741664429</v>
       </c>
       <c r="W96">
-        <v>0.2301097939190399</v>
+        <v>0.2301696908251553</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1206574656692132</v>
+        <v>0.1193873870832214</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9312,22 +9312,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2690951260613738</v>
+        <v>0.2709951260613738</v>
       </c>
       <c r="C97">
-        <v>-3.809485157822176</v>
+        <v>-3.872650808160286</v>
       </c>
       <c r="D97">
-        <v>1.149164842177825</v>
+        <v>1.139469191839714</v>
       </c>
       <c r="E97">
-        <v>4.932650000000001</v>
+        <v>4.986120000000001</v>
       </c>
       <c r="F97">
-        <v>5.079650000000001</v>
+        <v>5.133120000000001</v>
       </c>
       <c r="G97">
         <v>0.121</v>
@@ -9348,37 +9348,37 @@
         <v>0.143</v>
       </c>
       <c r="M97">
-        <v>1.19778147</v>
+        <v>1.210389696</v>
       </c>
       <c r="N97">
-        <v>-1.05478147</v>
+        <v>-1.067389696</v>
       </c>
       <c r="O97">
-        <v>-0.210956294</v>
+        <v>-0.2134779392</v>
       </c>
       <c r="P97">
-        <v>-0.8438251760000002</v>
+        <v>-0.8539117568000002</v>
       </c>
       <c r="Q97">
-        <v>-0.7868251760000001</v>
+        <v>-0.7969117568000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.008678395549526</v>
+        <v>1.249397994436908</v>
       </c>
       <c r="T97">
-        <v>18.26544735799472</v>
+        <v>22.83180919749342</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02387747741664429</v>
+        <v>0.02362875369355424</v>
       </c>
       <c r="W97">
-        <v>0.2301696908251553</v>
+        <v>0.2302283398790599</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1193873870832214</v>
+        <v>0.1181437684677712</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9394,22 +9394,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2709951260613738</v>
+        <v>0.2728951260613738</v>
       </c>
       <c r="C98">
-        <v>-3.872650808160286</v>
+        <v>-3.935654220444574</v>
       </c>
       <c r="D98">
-        <v>1.139469191839714</v>
+        <v>1.129935779555426</v>
       </c>
       <c r="E98">
-        <v>4.98612</v>
+        <v>5.03959</v>
       </c>
       <c r="F98">
-        <v>5.13312</v>
+        <v>5.186590000000001</v>
       </c>
       <c r="G98">
         <v>0.121</v>
@@ -9430,37 +9430,37 @@
         <v>0.143</v>
       </c>
       <c r="M98">
-        <v>1.210389696</v>
+        <v>1.222997922</v>
       </c>
       <c r="N98">
-        <v>-1.067389696</v>
+        <v>-1.079997922</v>
       </c>
       <c r="O98">
-        <v>-0.2134779392</v>
+        <v>-0.2159995844000001</v>
       </c>
       <c r="P98">
-        <v>-0.8539117568</v>
+        <v>-0.8639983376000002</v>
       </c>
       <c r="Q98">
-        <v>-0.7969117567999999</v>
+        <v>-0.8069983376000002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.249397994436905</v>
+        <v>1.650597325915873</v>
       </c>
       <c r="T98">
-        <v>22.83180919749335</v>
+        <v>30.44241226332447</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02362875369355425</v>
+        <v>0.02338515829465163</v>
       </c>
       <c r="W98">
-        <v>0.2302283398790599</v>
+        <v>0.2302857796741212</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1181437684677712</v>
+        <v>0.1169257914732581</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9476,22 +9476,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2728951260613738</v>
+        <v>0.2747951260613738</v>
       </c>
       <c r="C99">
-        <v>-3.935654220444574</v>
+        <v>-3.998499433000758</v>
       </c>
       <c r="D99">
-        <v>1.129935779555426</v>
+        <v>1.120560566999243</v>
       </c>
       <c r="E99">
-        <v>5.03959</v>
+        <v>5.09306</v>
       </c>
       <c r="F99">
-        <v>5.186590000000001</v>
+        <v>5.240060000000001</v>
       </c>
       <c r="G99">
         <v>0.121</v>
@@ -9512,37 +9512,37 @@
         <v>0.143</v>
       </c>
       <c r="M99">
-        <v>1.222997922</v>
+        <v>1.235606148</v>
       </c>
       <c r="N99">
-        <v>-1.079997922</v>
+        <v>-1.092606148</v>
       </c>
       <c r="O99">
-        <v>-0.2159995844000001</v>
+        <v>-0.2185212296000001</v>
       </c>
       <c r="P99">
-        <v>-0.8639983376000002</v>
+        <v>-0.8740849184000001</v>
       </c>
       <c r="Q99">
-        <v>-0.8069983376000002</v>
+        <v>-0.8170849184000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.650597325915873</v>
+        <v>2.45299598887381</v>
       </c>
       <c r="T99">
-        <v>30.44241226332447</v>
+        <v>45.66361839498671</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02338515829465163</v>
+        <v>0.02314653423042048</v>
       </c>
       <c r="W99">
-        <v>0.2302857796741212</v>
+        <v>0.2303420472284669</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1169257914732581</v>
+        <v>0.1157326711521024</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9558,22 +9558,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2747951260613738</v>
+        <v>0.2766951260613738</v>
       </c>
       <c r="C100">
-        <v>-3.998499433000758</v>
+        <v>-4.061190351231541</v>
       </c>
       <c r="D100">
-        <v>1.120560566999243</v>
+        <v>1.111339648768459</v>
       </c>
       <c r="E100">
-        <v>5.09306</v>
+        <v>5.14653</v>
       </c>
       <c r="F100">
-        <v>5.240060000000001</v>
+        <v>5.293530000000001</v>
       </c>
       <c r="G100">
         <v>0.121</v>
@@ -9594,37 +9594,37 @@
         <v>0.143</v>
       </c>
       <c r="M100">
-        <v>1.235606148</v>
+        <v>1.248214374</v>
       </c>
       <c r="N100">
-        <v>-1.092606148</v>
+        <v>-1.105214374</v>
       </c>
       <c r="O100">
-        <v>-0.2185212296000001</v>
+        <v>-0.2210428748000001</v>
       </c>
       <c r="P100">
-        <v>-0.8740849184000001</v>
+        <v>-0.8841714992000002</v>
       </c>
       <c r="Q100">
-        <v>-0.8170849184000001</v>
+        <v>-0.8271714992000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.45299598887381</v>
+        <v>4.860191977747619</v>
       </c>
       <c r="T100">
-        <v>45.66361839498671</v>
+        <v>91.32723678997341</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02314653423042048</v>
+        <v>0.02291273085435563</v>
       </c>
       <c r="W100">
-        <v>0.2303420472284669</v>
+        <v>0.230397178064543</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9632,91 +9632,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1157326711521024</v>
+        <v>0.1145636542717782</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2766951260613738</v>
-      </c>
-      <c r="C101">
-        <v>-4.061190351231541</v>
-      </c>
-      <c r="D101">
-        <v>1.111339648768459</v>
-      </c>
-      <c r="E101">
-        <v>5.14653</v>
-      </c>
-      <c r="F101">
-        <v>5.293530000000001</v>
-      </c>
-      <c r="G101">
-        <v>0.121</v>
-      </c>
-      <c r="H101">
-        <v>5.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.2</v>
-      </c>
-      <c r="K101">
-        <v>0.057</v>
-      </c>
-      <c r="L101">
-        <v>0.143</v>
-      </c>
-      <c r="M101">
-        <v>1.248214374</v>
-      </c>
-      <c r="N101">
-        <v>-1.105214374</v>
-      </c>
-      <c r="O101">
-        <v>-0.2210428748000001</v>
-      </c>
-      <c r="P101">
-        <v>-0.8841714992000002</v>
-      </c>
-      <c r="Q101">
-        <v>-0.8271714992000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.860191977747619</v>
-      </c>
-      <c r="T101">
-        <v>91.32723678997341</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02291273085435563</v>
-      </c>
-      <c r="W101">
-        <v>0.230397178064543</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1145636542717782</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
